--- a/output/StartPad_Initiative_Sponsor_List.xlsx
+++ b/output/StartPad_Initiative_Sponsor_List.xlsx
@@ -12,9 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PACKAGES" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IN-KIND MENU" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WHY THEY JOIN" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="THE NUMBERS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="THE SIX MONTHS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COVERAGE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COVERAGE" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'INVITATION LIST'!$A$1:$V$104</definedName>
@@ -25,11 +23,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0x"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,15 +104,6 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
-    <font>
-      <color rgb="003A4050"/>
-      <sz val="9.5"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="006B7A74"/>
-      <sz val="9.5"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -186,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -265,68 +253,30 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -694,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -820,111 +770,118 @@
     <row r="18" ht="26" customHeight="1">
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Full coalition value if every capped slot sells: $1,440,000. The wave is planned at 50% fill, which is $720,000, and that is the budget the funnel in the framework is quoted at.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
+          <t>Full coalition value if every capped slot sells: $381,000, which is EGP 20,276,820. The wave is planned at 50% fill, which is $190,500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="39" customHeight="1">
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>At that budget the wave reaches 1,200,000 people, registers 198,000 first-time founders, puts 19,393 of them through all fifteen missions, and leaves 71,359 ideas in the bank.</t>
+          <t>At that budget the wave reaches 1,200,000 people, registers 198,000 first-time founders, puts 20,100 of them through all fifteen missions at $5 each, runs 30 in-person cohorts at $3,000 each, and leaves 71,359 ideas in the bank.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="C20" s="4" t="inlineStr">
         <is>
+          <t>The full budget, the events, the field operations and what StartPad gets back are in the companion workbook: StartPad_Initiative_Budget.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="C21" s="4" t="inlineStr">
+        <is>
           <t>The million is not a six-month number. The framework says so in the arithmetic, and so should anyone using this list.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>HOW TO WORK IT</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Founding Partners first, and do not announce until three have signed. A coalition with nobody in it is a hard sell; a coalition with three recognisable names in it sells itself to the next twenty.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Community supporters second, and before the summer, because student leadership turns over in July and August. They cost nothing and they are the highest converting reach in the whole plan.</t>
+          <t>Founding Partners first, and do not announce until three have signed. A coalition with nobody in it is a hard sell; a coalition with three recognisable names in it sells itself to the next twenty.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="C25" s="4" t="inlineStr">
         <is>
+          <t>Community supporters second, and before the summer, because student leadership turns over in July and August. They cost nothing and they are the highest converting reach in the whole plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="C26" s="4" t="inlineStr">
+        <is>
           <t>NGO and development partners third. They bring reach and governorates rather than money, and several of them will want to co-apply for donor funding, which is a slower and larger conversation than sponsorship.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>THE COLUMNS YOU FILL IN</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="C28" s="4" t="inlineStr">
+    <row r="29" ht="26" customHeight="1">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Stage, owner, pledged amount, next action, next date and notes. Pledged amount is what makes the COVERAGE sheet mean anything, so fill it in even when it is a guess.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>CONFIDENCE, UNCHANGED FROM THE REGISTRY</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Organisation and focus confirmed in published sources.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Established organisation; the specific programme or route changes between cycles and must be re-checked.</t>
+          <t>Organisation and focus confirmed in published sources.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="B33" s="5" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Established organisation; the specific programme or route changes between cycles and must be re-checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
           <t>low</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>A reasoned prospect. Verify before spending a meeting.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="C34" s="4" t="inlineStr">
+    <row r="35" ht="26" customHeight="1">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>No individual's name, email address or phone number appears anywhere in this file, for the same reason as in the registry: a stale contact burns the introduction.</t>
         </is>
@@ -10229,7 +10186,7 @@
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>$150,000</t>
+          <t>$40,000</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
@@ -10347,7 +10304,7 @@
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>$75,000</t>
+          <t>$20,000</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -10441,7 +10398,7 @@
       </c>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>$30,000</t>
+          <t>$8,000</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -10475,7 +10432,7 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>Cohorts, a local showcase and a governorate report with named participants.</t>
+          <t>Two cohorts, a local showcase and a governorate report with named participants.</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10468,7 @@
       </c>
       <c r="C28" s="22" t="inlineStr">
         <is>
-          <t>$12,000</t>
+          <t>$3,000</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -10603,7 +10560,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>Credited at the tier their contribution values at, with the same benefits. Media airtime at a rate card value of $75,000 is a Lead Partner.</t>
+          <t>Credited at the tier their contribution values at, with the same benefits. Media airtime at a rate card value of EGP 1.1 million is a Lead Partner.</t>
         </is>
       </c>
     </row>
@@ -11541,936 +11498,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="78" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Wave 1, March to August 2027: the arithmetic</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="19" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Built from the coalition rather than asserted. Change a channel and the funnel moves.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>WHERE THE REACH COMES FROM</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Partners</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Reach each</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Registers</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Why</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="37.2" customHeight="1">
-      <c r="B6" s="28" t="inlineStr">
-        <is>
-          <t>Community supporter chapters</t>
-        </is>
-      </c>
-      <c r="C6" s="29" t="n">
-        <v>150</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E6" s="30" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F6" s="31" t="inlineStr">
-        <is>
-          <t>150 university and youth chapters, each reaching about 3,000 members and fellow students. The highest converting channel because the invitation comes from someone the student already knows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="B7" s="28" t="inlineStr">
-        <is>
-          <t>CSR sponsor channels</t>
-        </is>
-      </c>
-      <c r="C7" s="29" t="n">
-        <v>24</v>
-      </c>
-      <c r="D7" s="29" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E7" s="30" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F7" s="31" t="inlineStr">
-        <is>
-          <t>24 sponsors reaching their own employees, customers, retail networks, social audiences and foundation beneficiaries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="28" t="inlineStr">
-        <is>
-          <t>NGO and development partner networks</t>
-        </is>
-      </c>
-      <c r="C8" s="29" t="n">
-        <v>18</v>
-      </c>
-      <c r="D8" s="29" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E8" s="30" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F8" s="31" t="inlineStr">
-        <is>
-          <t>18 partners reaching their branch networks, beneficiary lists and governorate programmes, mostly outside Cairo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
-        <is>
-          <t>Mission Zero, press and organic</t>
-        </is>
-      </c>
-      <c r="C9" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="29" t="n">
-        <v>90000</v>
-      </c>
-      <c r="E9" s="30" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F9" s="31" t="inlineStr">
-        <is>
-          <t>The founder podcast, launch and showcase press, and organic traffic to the platform.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>Total reach</t>
-        </is>
-      </c>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="34">
-        <f>SUMPRODUCT(C6:C9,D6:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="33" t="n"/>
-      <c r="F10" s="33" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>THE FUNNEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="35" t="inlineStr">
-        <is>
-          <t>People reached</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="F13" s="37" t="inlineStr">
-        <is>
-          <t>Sum of every channel's reach, before anybody registers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="35" t="inlineStr">
-        <is>
-          <t>Registered founders</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="n">
-        <v>198000</v>
-      </c>
-      <c r="F14" s="37" t="inlineStr">
-        <is>
-          <t>Accounts created on the platform during the wave.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>Mission 01 completed</t>
-        </is>
-      </c>
-      <c r="C15" s="36" t="n">
-        <v>104940</v>
-      </c>
-      <c r="F15" s="37" t="inlineStr">
-        <is>
-          <t>The first real act of work, and the first honest number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>Missions 01 to 03 completed</t>
-        </is>
-      </c>
-      <c r="C16" s="36" t="n">
-        <v>58766</v>
-      </c>
-      <c r="F16" s="37" t="inlineStr">
-        <is>
-          <t>The end of the free tier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>Sponsored full journeys, all 15 missions</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="n">
-        <v>19393</v>
-      </c>
-      <c r="F17" s="37" t="inlineStr">
-        <is>
-          <t>What sponsorship actually buys.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>In-person cohort seats</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="n">
-        <v>2909</v>
-      </c>
-      <c r="F18" s="37" t="inlineStr">
-        <is>
-          <t>Delivered in cohorts of 30, with certified facilitators.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="35" t="inlineStr">
-        <is>
-          <t>Cohorts run</t>
-        </is>
-      </c>
-      <c r="C19" s="36" t="n">
-        <v>97</v>
-      </c>
-      <c r="F19" s="37" t="inlineStr">
-        <is>
-          <t>Each one is six days, a room, a facilitator and a showcase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="35" t="inlineStr">
-        <is>
-          <t>Ideas in the bank</t>
-        </is>
-      </c>
-      <c r="C20" s="36" t="n">
-        <v>71359</v>
-      </c>
-      <c r="F20" s="37" t="inlineStr">
-        <is>
-          <t>Consented, structured, and the asset the wave leaves behind.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>Ventures trading at month 12</t>
-        </is>
-      </c>
-      <c r="C21" s="36" t="n">
-        <v>1939</v>
-      </c>
-      <c r="F21" s="37" t="inlineStr">
-        <is>
-          <t>Measured twelve months after the wave closes, not at the end of it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>WHAT IT COSTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="38" t="inlineStr">
-        <is>
-          <t>Coalition value if every capped slot sells</t>
-        </is>
-      </c>
-      <c r="C24" s="39" t="n">
-        <v>1440000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="35" t="inlineStr">
-        <is>
-          <t>Wave 1 budget at 50% fill</t>
-        </is>
-      </c>
-      <c r="C25" s="40" t="n">
-        <v>720000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="38" t="inlineStr">
-        <is>
-          <t>Delivery: facilitators, cohorts, venues, travel</t>
-        </is>
-      </c>
-      <c r="C27" s="30" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="D27" s="29" t="n">
-        <v>273600</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="38" t="inlineStr">
-        <is>
-          <t>Platform, AI review and infrastructure</t>
-        </is>
-      </c>
-      <c r="C28" s="30" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D28" s="29" t="n">
-        <v>129600</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="38" t="inlineStr">
-        <is>
-          <t>Community activation: chapters, ambassadors, campus</t>
-        </is>
-      </c>
-      <c r="C29" s="30" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D29" s="29" t="n">
-        <v>86400</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="38" t="inlineStr">
-        <is>
-          <t>Content, localisation and Arabic production</t>
-        </is>
-      </c>
-      <c r="C30" s="30" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D30" s="29" t="n">
-        <v>72000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="38" t="inlineStr">
-        <is>
-          <t>Events: launch, governorate showcases, national demo day</t>
-        </is>
-      </c>
-      <c r="C31" s="30" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="D31" s="29" t="n">
-        <v>64800</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="38" t="inlineStr">
-        <is>
-          <t>Programme management and overhead</t>
-        </is>
-      </c>
-      <c r="C32" s="30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D32" s="29" t="n">
-        <v>50400.00000000001</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="38" t="inlineStr">
-        <is>
-          <t>Measurement, evaluation and reporting</t>
-        </is>
-      </c>
-      <c r="C33" s="30" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D33" s="29" t="n">
-        <v>43200</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>COST PER OUTCOME</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="38" t="inlineStr">
-        <is>
-          <t>Cost per person reached</t>
-        </is>
-      </c>
-      <c r="C36" s="41" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="38" t="inlineStr">
-        <is>
-          <t>Cost per registered founder</t>
-        </is>
-      </c>
-      <c r="C37" s="41" t="n">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="38" t="inlineStr">
-        <is>
-          <t>Cost per founder completing the free tier</t>
-        </is>
-      </c>
-      <c r="C38" s="41" t="n">
-        <v>12.25</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="38" t="inlineStr">
-        <is>
-          <t>Cost per sponsored full journey</t>
-        </is>
-      </c>
-      <c r="C39" s="41" t="n">
-        <v>37.13</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="38" t="inlineStr">
-        <is>
-          <t>Cost per in-person seat</t>
-        </is>
-      </c>
-      <c r="C40" s="41" t="n">
-        <v>247.51</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="38" t="inlineStr">
-        <is>
-          <t>Cost per venture trading at month 12</t>
-        </is>
-      </c>
-      <c r="C41" s="41" t="n">
-        <v>371.27</v>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="B43" s="42" t="inlineStr">
-        <is>
-          <t>The cost per sponsored full journey is above the $15 list price of a Pro subscription because it carries its share of facilitation, community activation, content, events and measurement, not only the licence.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="76" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Wave 1, March to August 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="19" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Why this window and not another, month by month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>BEFORE THE WAVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24.8" customHeight="1">
-      <c r="B5" s="43" t="inlineStr">
-        <is>
-          <t>October 2026</t>
-        </is>
-      </c>
-      <c r="C5" s="44" t="inlineStr">
-        <is>
-          <t>Assemble the coalition</t>
-        </is>
-      </c>
-      <c r="E5" s="45" t="inlineStr">
-        <is>
-          <t>First approaches to the Founding and Lead tiers, and to the patron ministries. Nothing is announced until three Founding Partners have signed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24.8" customHeight="1">
-      <c r="B6" s="43" t="inlineStr">
-        <is>
-          <t>November 2026</t>
-        </is>
-      </c>
-      <c r="C6" s="44" t="inlineStr">
-        <is>
-          <t>Patron endorsement</t>
-        </is>
-      </c>
-      <c r="E6" s="45" t="inlineStr">
-        <is>
-          <t>Memoranda with the national initiative and the relevant ministries. These cost them nothing and are worth more than their money.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="37.2" customHeight="1">
-      <c r="B7" s="43" t="inlineStr">
-        <is>
-          <t>December 2026</t>
-        </is>
-      </c>
-      <c r="C7" s="44" t="inlineStr">
-        <is>
-          <t>Community supporters</t>
-        </is>
-      </c>
-      <c r="E7" s="45" t="inlineStr">
-        <is>
-          <t>Charters signed with the youth foundations and student organisations. Their leadership years are already underway, so this is the right moment, not the summer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24.8" customHeight="1">
-      <c r="B8" s="43" t="inlineStr">
-        <is>
-          <t>January 2027</t>
-        </is>
-      </c>
-      <c r="C8" s="44" t="inlineStr">
-        <is>
-          <t>Certify the facilitators</t>
-        </is>
-      </c>
-      <c r="E8" s="45" t="inlineStr">
-        <is>
-          <t>The facilitator pool and the chapter leadership are certified before the wave opens, not during it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24.8" customHeight="1">
-      <c r="B9" s="43" t="inlineStr">
-        <is>
-          <t>February 2027</t>
-        </is>
-      </c>
-      <c r="C9" s="44" t="inlineStr">
-        <is>
-          <t>Localise and rehearse</t>
-        </is>
-      </c>
-      <c r="E9" s="45" t="inlineStr">
-        <is>
-          <t>Arabic content finalised, platform load tested, two rehearsal cohorts run with a partner NGO. Ramadan month; no public launch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>THE WAVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>When</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>What it is</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>What happens</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Where it should be by month end</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="37.2" customHeight="1">
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Month 1</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>March 2027</t>
-        </is>
-      </c>
-      <c r="D13" s="28" t="inlineStr">
-        <is>
-          <t>Launch</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>National launch after Eid al-Fitr, with the coalition on stage and the patron ministries present. Platform opens. All 150 chapters activate in the same week, which is the only way a launch number looks like a launch.</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>59,400 registered; 5 cohorts</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Month 2</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>April 2027</t>
-        </is>
-      </c>
-      <c r="D14" s="28" t="inlineStr">
-        <is>
-          <t>Campus peak</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>The strongest campus month of the Egyptian year. Ambassador recruitment, the first governorate waves, and the first cohorts in volume.</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>120,780 registered; 30 cohorts</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="37.2" customHeight="1">
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Month 3</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>May 2027</t>
-        </is>
-      </c>
-      <c r="D15" s="28" t="inlineStr">
-        <is>
-          <t>Exams, so go online</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>University exams run through May. Campus activity stops and the wave moves to the NGO networks, the youth centres and online delivery. Mid-wave report to the partner council.</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>160,380 registered; 7 cohorts</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Month 4</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>June 2027</t>
-        </is>
-      </c>
-      <c r="D16" s="28" t="inlineStr">
-        <is>
-          <t>Summer opens</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>Exams end mid-month and the summer intensives begin, which is when young people have six consecutive days to give.</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>180,180 registered; 25 cohorts</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="37.2" customHeight="1">
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Month 5</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>July 2027</t>
-        </is>
-      </c>
-      <c r="D17" s="28" t="inlineStr">
-        <is>
-          <t>Peak delivery</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>The heaviest in-person month of the wave, with governorate showcases running in parallel. The first national read of the ideas bank goes to partners.</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>192,060 registered; 30 cohorts</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="49.6" customHeight="1">
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Month 6</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>August 2027</t>
-        </is>
-      </c>
-      <c r="D18" s="28" t="inlineStr">
-        <is>
-          <t>Showcase and close</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>National showcase and demo day: the best teams from every governorate, in front of the coalition, the ministries and the press. Closing report, independent evaluation commissioned, and the extension decision taken with the partners in the room.</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>198,000 registered</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>AND WHEN IS THE MILLION</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="24.8" customHeight="1">
-      <c r="B22" s="46" t="inlineStr">
-        <is>
-          <t>Wave 1</t>
-        </is>
-      </c>
-      <c r="C22" s="47" t="inlineStr">
-        <is>
-          <t>March to August 2027</t>
-        </is>
-      </c>
-      <c r="D22" s="47" t="inlineStr">
-        <is>
-          <t>Egypt, 12 governorates</t>
-        </is>
-      </c>
-      <c r="E22" s="47" t="inlineStr">
-        <is>
-          <t>The wave this framework covers. Proves the unit economics and builds the coalition.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24.8" customHeight="1">
-      <c r="B23" s="46" t="inlineStr">
-        <is>
-          <t>Wave 2</t>
-        </is>
-      </c>
-      <c r="C23" s="47" t="inlineStr">
-        <is>
-          <t>September 2027 to February 2028</t>
-        </is>
-      </c>
-      <c r="D23" s="47" t="inlineStr">
-        <is>
-          <t>Egypt, 20 governorates</t>
-        </is>
-      </c>
-      <c r="E23" s="47" t="inlineStr">
-        <is>
-          <t>The extension. Same coalition, wider geography, lower cost per founder because the facilitator pool and the chapters already exist.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="24.8" customHeight="1">
-      <c r="B24" s="46" t="inlineStr">
-        <is>
-          <t>Wave 3</t>
-        </is>
-      </c>
-      <c r="C24" s="47" t="inlineStr">
-        <is>
-          <t>March to August 2028</t>
-        </is>
-      </c>
-      <c r="D24" s="47" t="inlineStr">
-        <is>
-          <t>Egypt, all 27 governorates</t>
-        </is>
-      </c>
-      <c r="E24" s="47" t="inlineStr">
-        <is>
-          <t>National coverage, with the schools and technical education systems carrying volume the university system cannot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="37.2" customHeight="1">
-      <c r="B25" s="46" t="inlineStr">
-        <is>
-          <t>Wave 4</t>
-        </is>
-      </c>
-      <c r="C25" s="47" t="inlineStr">
-        <is>
-          <t>September 2028 to February 2029</t>
-        </is>
-      </c>
-      <c r="D25" s="47" t="inlineStr">
-        <is>
-          <t>Egypt, plus the region</t>
-        </is>
-      </c>
-      <c r="E25" s="47" t="inlineStr">
-        <is>
-          <t>The million is crossed inside this wave on these rates. Anything faster needs either a national initiative mandating participation or a step change in sponsorship.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12530,112 +11557,112 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="48" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Founding Partner</t>
         </is>
       </c>
-      <c r="C5" s="49" t="n">
+      <c r="C5" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="49" t="n">
+      <c r="D5" s="29" t="n">
         <v>22</v>
       </c>
-      <c r="E5" s="50">
+      <c r="E5" s="30">
         <f>D5/C5</f>
         <v/>
       </c>
-      <c r="F5" s="29" t="n">
-        <v>150000</v>
-      </c>
-      <c r="G5" s="29" t="n">
-        <v>450000</v>
+      <c r="F5" s="31" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G5" s="31" t="n">
+        <v>120000</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="48" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Lead Partner</t>
         </is>
       </c>
-      <c r="C6" s="49" t="n">
+      <c r="C6" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="49" t="n">
+      <c r="D6" s="29" t="n">
         <v>36</v>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="30">
         <f>D6/C6</f>
         <v/>
       </c>
-      <c r="F6" s="29" t="n">
-        <v>75000</v>
-      </c>
-      <c r="G6" s="29" t="n">
-        <v>450000</v>
+      <c r="F6" s="31" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <v>120000</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="48" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Governorate Partner</t>
         </is>
       </c>
-      <c r="C7" s="49" t="n">
+      <c r="C7" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="49" t="n">
+      <c r="D7" s="29" t="n">
         <v>24</v>
       </c>
-      <c r="E7" s="50">
+      <c r="E7" s="30">
         <f>D7/C7</f>
         <v/>
       </c>
-      <c r="F7" s="29" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G7" s="29" t="n">
-        <v>360000</v>
+      <c r="F7" s="31" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G7" s="31" t="n">
+        <v>96000</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="48" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Mission Partner</t>
         </is>
       </c>
-      <c r="C8" s="49" t="n">
+      <c r="C8" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="D8" s="51" t="n">
+      <c r="D8" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="E8" s="52">
+      <c r="E8" s="33">
         <f>D8/C8</f>
         <v/>
       </c>
-      <c r="F8" s="29" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G8" s="29" t="n">
-        <v>180000</v>
+      <c r="F8" s="31" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G8" s="31" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9" s="53">
+      <c r="C9" s="35">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="53">
+      <c r="D9" s="35">
         <f>SUM(D5:D8)</f>
         <v/>
       </c>
-      <c r="G9" s="53">
+      <c r="G9" s="35">
         <f>SUM(G5:G8)</f>
         <v/>
       </c>
@@ -12648,57 +11675,57 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Organisations invited</t>
         </is>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="37">
         <f>COUNTIF('INVITATION LIST'!Q2:Q104,"&lt;&gt;Not invited")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="37">
         <f>COUNTIF('INVITATION LIST'!Q2:Q104,"Signed")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>Pledged, USD</t>
         </is>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="37">
         <f>SUM('INVITATION LIST'!S2:S104)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>Wave 1 budget needed</t>
         </is>
       </c>
-      <c r="C15" s="36">
-        <f>720000.0</f>
+      <c r="C15" s="37">
+        <f>190500.0</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="C16" s="36">
-        <f>720000.0-SUM('INVITATION LIST'!S2:S104)</f>
+      <c r="C16" s="37">
+        <f>190500.0-SUM('INVITATION LIST'!S2:S104)</f>
         <v/>
       </c>
     </row>

--- a/output/StartPad_Initiative_Sponsor_List.xlsx
+++ b/output/StartPad_Initiative_Sponsor_List.xlsx
@@ -174,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -261,12 +261,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -713,7 +707,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Egyptian and international NGOs, philanthropic foundations, development agencies and UN agencies working on youth, livelihoods, employment or education.  GIVES: Reach into their own beneficiary networks and governorates, staff time, venues, co-funding where they hold a relevant budget, and co-applicant status on joint proposals.  GETS: The method and the facilitator certification for their own staff, which they keep afterwards, a measured evidence base for their next donor proposal, and access to the sponsor coalition.</t>
+          <t>Egyptian and international NGOs, philanthropic foundations, development agencies and UN agencies working on youth, livelihoods, employment or education.  GIVES: Reach into their own beneficiary networks and governorates, staff time, venues, co-funding where they hold a relevant budget, and co-applicant status on joint proposals.  GETS: The method for their own beneficiaries, their staff trained to host sessions, a measured evidence base for their next donor proposal, and access to the sponsor coalition.</t>
         </is>
       </c>
     </row>
@@ -725,7 +719,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Youth foundations and student organisations with members on campuses: Enactus, INJAZ, AIESEC, JCI, Hult Prize chapters, technical student branches and the youth volunteer networks.  GIVES: Their students and members, their chapters as local hosts, and their leadership as certified facilitators.  GETS: The full programme free for every member, a credential their leadership keeps after their term ends, a national stage at the showcase, better-prepared teams for their own competitions, and their own chapter's data.</t>
+          <t>Youth foundations and student organisations with members on campuses: Enactus, INJAZ, AIESEC, JCI, Hult Prize chapters, technical student branches and the youth volunteer networks.  GIVES: Their students and members, their chapters as hosts for info sessions, and their leadership trained to run them.  GETS: The full programme free for every member, a credential their leadership keeps after their term ends, a national stage at the showcase, better-prepared teams for their own competitions, and their own chapter's data.</t>
         </is>
       </c>
     </row>
@@ -770,28 +764,28 @@
     <row r="18" ht="26" customHeight="1">
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Full coalition value if every capped slot sells: $381,000, which is EGP 20,276,820. The wave is planned at 50% fill, which is $190,500.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="39" customHeight="1">
+          <t>The wave costs $200,000, which is EGP 10,644,000, and it is funded entirely by the organisations on this list. StartPad puts in no cash at all and takes no margin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>At that budget the wave reaches 1,200,000 people, registers 198,000 first-time founders, puts 20,100 of them through all fifteen missions at $5 each, runs 30 in-person cohorts at $3,000 each, and leaves 71,359 ideas in the bank.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
+          <t>The three cash tiers raise $250,000 if every slot sells, so the coalition can lose four or five conversations and still fund the wave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="39" customHeight="1">
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>The full budget, the events, the field operations and what StartPad gets back are in the companion workbook: StartPad_Initiative_Budget.xlsx.</t>
+          <t>At that budget the initiative registers 1,000,000 entrepreneurs at $0.20 a head, puts 27,000 of them through all fifteen missions, and leaves 306,000 ideas in the bank. Everything is online and free, there are no paid cohorts, and offline sessions happen only where a partner asks for one and hosts it.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>The million is not a six-month number. The framework says so in the arithmetic, and so should anyone using this list.</t>
+          <t>The full budget and what StartPad gets back are in the companion workbook: StartPad_Initiative_Budget.xlsx.</t>
         </is>
       </c>
     </row>
@@ -805,21 +799,21 @@
     <row r="24" ht="26" customHeight="1">
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Founding Partners first, and do not announce until three have signed. A coalition with nobody in it is a hard sell; a coalition with three recognisable names in it sells itself to the next twenty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
+          <t>Founding Partners first, and do not announce until both have signed. A coalition with nobody in it is a hard sell; a coalition with two recognisable names in it sells itself to the next fifteen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="39" customHeight="1">
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Community supporters second, and before the summer, because student leadership turns over in July and August. They cost nothing and they are the highest converting reach in the whole plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1">
+          <t>Community supporters second, and before the summer, because student leadership turns over in July and August. They cost nothing, they are the highest converting reach in the whole plan, and the referral loop runs on them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="39" customHeight="1">
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>NGO and development partners third. They bring reach and governorates rather than money, and several of them will want to co-apply for donor funding, which is a slower and larger conversation than sponsorship.</t>
+          <t>NGO and development partners third. They bring reach, governorates and the venues for offline info sessions rather than money, and several will want to co-apply for donor funding, which is a slower and larger conversation.</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1064,12 @@
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I2" s="10" t="inlineStr">
@@ -1158,12 +1152,12 @@
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
@@ -1246,12 +1240,12 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr">
@@ -1334,12 +1328,12 @@
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1393,7 +1387,7 @@
       <c r="U5" s="14" t="n"/>
       <c r="V5" s="14" t="n"/>
     </row>
-    <row r="6" ht="61" customHeight="1">
+    <row r="6" ht="48.8" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -1422,12 +1416,12 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -1510,12 +1504,12 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -1577,7 +1571,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -1598,12 +1592,12 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -1665,7 +1659,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1686,12 +1680,12 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -1745,7 +1739,7 @@
       <c r="U9" s="14" t="n"/>
       <c r="V9" s="14" t="n"/>
     </row>
-    <row r="10" ht="61" customHeight="1">
+    <row r="10" ht="48.8" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -1753,58 +1747,58 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Nestle Egypt</t>
+          <t>Madinet Masr</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>Food and beverage</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Greater Cairo</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>Nestle Needs YOUth, a global youth employability and entrepreneurship commitment, plus agricultural and community programmes.</t>
+          <t>Community and youth programmes, and a named private-sector partner of the Orange Corners entrepreneurship programme in Egypt.</t>
         </is>
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>Young people reached, jobs and businesses created, reported into the global commitment.</t>
+          <t>Association with a credible entrepreneurship programme and community development around their developments.</t>
         </is>
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>Corporate communications and public affairs manager, who typically owns Needs YOUth locally</t>
+          <t>Corporate communications or sustainability lead</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>Direct to corporate affairs, naming the global commitment. AmCham is the warm route.</t>
+          <t>Through Orange Corners Egypt, where the relationship already exists.</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>Calendar year, with global commitment reporting in the first quarter.</t>
+          <t>Calendar year.</t>
         </is>
       </c>
       <c r="N10" s="11" t="inlineStr">
@@ -1812,14 +1806,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>medium</t>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
       <c r="P10" s="10" t="inlineStr">
         <is>
-          <t>Needs YOUth is a long-standing global programme; the Egypt country plan and partner list need confirming.</t>
+          <t>Confirmed this session: named as a partner celebrating Orange Corners Egypt graduates in Delta and Upper Egypt.</t>
         </is>
       </c>
       <c r="Q10" s="13" t="inlineStr">
@@ -1833,7 +1827,7 @@
       <c r="U10" s="14" t="n"/>
       <c r="V10" s="14" t="n"/>
     </row>
-    <row r="11" ht="73.19999999999999" customHeight="1">
+    <row r="11" ht="48.8" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -1841,62 +1835,58 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Orange Egypt</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>أورانج مصر</t>
-        </is>
-      </c>
+          <t>Nestle Egypt</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Food and beverage</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>National, with a Delta and Upper Egypt focus</t>
+          <t>National</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>Orange Social Venture Prize, long-running Enactus Egypt sponsorship, and Orange Digital Centers. Entrepreneurship is a standing line, not a one-off campaign.</t>
+          <t>Nestle Needs YOUth, a global youth employability and entrepreneurship commitment, plus agricultural and community programmes.</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>Visible national impact, a pipeline of ventures for the Social Venture Prize, and governorate coverage outside Cairo.</t>
+          <t>Young people reached, jobs and businesses created, reported into the global commitment.</t>
         </is>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>CSR and sustainability manager, with the Orange Digital Center lead as the operational counterpart</t>
+          <t>Corporate communications and public affairs manager, who typically owns Needs YOUth locally</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>Orange Digital Center Cairo is the open door: it hosts programmes and its team can route an offer internally. Enactus Egypt can introduce.</t>
+          <t>Direct to corporate affairs, naming the global commitment. AmCham is the warm route.</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>Calendar year budgeting, with the Social Venture Prize local round running in the first half of the year.</t>
+          <t>Calendar year, with global commitment reporting in the first quarter.</t>
         </is>
       </c>
       <c r="N11" s="11" t="inlineStr">
@@ -1904,14 +1894,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="O11" s="12" t="inlineStr">
-        <is>
-          <t>high</t>
+      <c r="O11" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>Confirmed this session: twenty consecutive years sponsoring Enactus Egypt, and three Egyptian startups advanced to the Social Venture Prize international stage in the sixteenth edition.</t>
+          <t>Needs YOUth is a long-standing global programme; the Egypt country plan and partner list need confirming.</t>
         </is>
       </c>
       <c r="Q11" s="13" t="inlineStr">
@@ -1933,58 +1923,62 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Shell Egypt</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr"/>
+          <t>Orange Egypt</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>أورانج مصر</t>
+        </is>
+      </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>Oil and gas</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>National, with a Delta and Upper Egypt focus</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>Shell Intilaaqah, a long-running youth enterprise development programme, alongside STEM and scholarship work.</t>
+          <t>Orange Social Venture Prize, long-running Enactus Egypt sponsorship, and Orange Digital Centers. Entrepreneurship is a standing line, not a one-off campaign.</t>
         </is>
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>Continuity of a flagship programme, cost per beneficiary, and measurable business creation.</t>
+          <t>Visible national impact, a pipeline of ventures for the Social Venture Prize, and governorate coverage outside Cairo.</t>
         </is>
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>Social investment or social performance manager</t>
+          <t>CSR and sustainability manager, with the Orange Digital Center lead as the operational counterpart</t>
         </is>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>Direct to social investment. Their current implementing partner can also sub-contract delivery, which is a faster first step.</t>
+          <t>Orange Digital Center Cairo is the open door: it hosts programmes and its team can route an offer internally. Enactus Egypt can introduce.</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>Calendar year, with social investment budgets set in the fourth quarter.</t>
+          <t>Calendar year budgeting, with the Social Venture Prize local round running in the first half of the year.</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
@@ -1992,14 +1986,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>medium</t>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
       <c r="P12" s="10" t="inlineStr">
         <is>
-          <t>Intilaaqah is a long-established Shell programme in several countries including Egypt. Confirm the Egypt cycle and current implementing partner before proposing.</t>
+          <t>Confirmed this session: twenty consecutive years sponsoring Enactus Egypt, and three Egyptian startups advanced to the Social Venture Prize international stage in the sixteenth edition.</t>
         </is>
       </c>
       <c r="Q12" s="13" t="inlineStr">
@@ -2013,7 +2007,7 @@
       <c r="U12" s="14" t="n"/>
       <c r="V12" s="14" t="n"/>
     </row>
-    <row r="13" ht="85.39999999999999" customHeight="1">
+    <row r="13" ht="73.19999999999999" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -2021,22 +2015,18 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Vodafone Egypt Foundation</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>مؤسسة فودافون مصر</t>
-        </is>
-      </c>
+          <t>Shell Egypt</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Oil and gas</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -2046,37 +2036,37 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>The CSR arm of Vodafone Egypt, registered as a foundation with the Ministry of Social Solidarity. Education, digital skills and youth empowerment, delivered partly through the Ta3limy e-learning platform.</t>
+          <t>Shell Intilaaqah, a long-running youth enterprise development programme, alongside STEM and scholarship work.</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Reach numbers at national scale, a digital asset that keeps working after the money is spent, and Egyptian youth employability they can report to group CSR in London.</t>
+          <t>Continuity of a flagship programme, cost per beneficiary, and measurable business creation.</t>
         </is>
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>Foundation director, and the head of the youth or education pillar beneath them</t>
+          <t>Social investment or social performance manager</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>The foundation page on web.vodafone.com.eg carries the registered entity and its contact channel. Warmer route: an NGO already implementing for them, or the AmCham CSR committee.</t>
+          <t>Direct to social investment. Their current implementing partner can also sub-contract delivery, which is a faster first step.</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>Vodafone runs an April to March financial year, so the budget conversation is strongest between November and January.</t>
+          <t>Calendar year, with social investment budgets set in the fourth quarter.</t>
         </is>
       </c>
       <c r="N13" s="11" t="inlineStr">
@@ -2084,14 +2074,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>high</t>
+      <c r="O13" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="P13" s="10" t="inlineStr">
         <is>
-          <t>Confirmed this session: the foundation ran a Spark Bootcamp with the Momken platform for 40 early-stage tech entrepreneurs, with content folded into Ta3limy. Verify the current cohort cycle before quoting.</t>
+          <t>Intilaaqah is a long-established Shell programme in several countries including Egypt. Confirm the Egypt cycle and current implementing partner before proposing.</t>
         </is>
       </c>
       <c r="Q13" s="13" t="inlineStr">
@@ -2105,7 +2095,7 @@
       <c r="U13" s="14" t="n"/>
       <c r="V13" s="14" t="n"/>
     </row>
-    <row r="14" ht="61" customHeight="1">
+    <row r="14" ht="85.39999999999999" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -2113,73 +2103,77 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Apache Egypt and Khalda Petroleum</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
+          <t>Vodafone Egypt Foundation</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>مؤسسة فودافون مصر</t>
+        </is>
+      </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Oil and gas</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>Western Desert and national</t>
+          <t>National</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>One of the largest private social investment records in Egypt, historically centred on building and equipping schools for girls.</t>
+          <t>The CSR arm of Vodafone Egypt, registered as a foundation with the Ministry of Social Solidarity. Education, digital skills and youth empowerment, delivered partly through the Ta3limy e-learning platform.</t>
         </is>
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>Continuity of an education legacy, and girls' education and employability outcomes.</t>
+          <t>Reach numbers at national scale, a digital asset that keeps working after the money is spent, and Egyptian youth employability they can report to group CSR in London.</t>
         </is>
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>Public affairs or community development manager</t>
+          <t>Foundation director, and the head of the youth or education pillar beneath them</t>
         </is>
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>Direct. The schools themselves are also a route upward.</t>
+          <t>The foundation page on web.vodafone.com.eg carries the registered entity and its contact channel. Warmer route: an NGO already implementing for them, or the AmCham CSR committee.</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>Calendar year.</t>
+          <t>Vodafone runs an April to March financial year, so the budget conversation is strongest between November and January.</t>
         </is>
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
       <c r="P14" s="10" t="inlineStr">
         <is>
-          <t>The girls' education programme is a well-known, long-running commitment. Current scale and focus need confirming.</t>
+          <t>Confirmed this session: the foundation ran a Spark Bootcamp with the Momken platform for 40 early-stage tech entrepreneurs, with content folded into Ta3limy. Verify the current cohort cycle before quoting.</t>
         </is>
       </c>
       <c r="Q14" s="13" t="inlineStr">
@@ -2193,7 +2187,7 @@
       <c r="U14" s="14" t="n"/>
       <c r="V14" s="14" t="n"/>
     </row>
-    <row r="15" ht="61" customHeight="1">
+    <row r="15" ht="48.8" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -2201,53 +2195,53 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Arab African International Bank (AAIB)</t>
+          <t>Apache Egypt and Khalda Petroleum</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr"/>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Oil and gas</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Western Desert and national</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>One of the more sustainability-forward Egyptian banks, with a dedicated sustainability function and published commitments.</t>
+          <t>One of the largest private social investment records in Egypt, historically centred on building and equipping schools for girls.</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>Sustainability reporting content and visible youth impact.</t>
+          <t>Continuity of an education legacy, and girls' education and employability outcomes.</t>
         </is>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>Chief sustainability officer or head of sustainable development</t>
+          <t>Public affairs or community development manager</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>Direct, through the sustainability function rather than marketing.</t>
+          <t>Direct. The schools themselves are also a route upward.</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
@@ -2267,7 +2261,7 @@
       </c>
       <c r="P15" s="10" t="inlineStr">
         <is>
-          <t>Sustainability positioning is established; the specific budget line is unconfirmed.</t>
+          <t>The girls' education programme is a well-known, long-running commitment. Current scale and focus need confirming.</t>
         </is>
       </c>
       <c r="Q15" s="13" t="inlineStr">
@@ -2281,7 +2275,7 @@
       <c r="U15" s="14" t="n"/>
       <c r="V15" s="14" t="n"/>
     </row>
-    <row r="16" ht="61" customHeight="1">
+    <row r="16" ht="48.8" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -2289,12 +2283,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Bank of Alexandria (Intesa Sanpaolo)</t>
+          <t>Arab African International Bank (AAIB)</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr"/>
@@ -2310,37 +2304,37 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>Micro and small enterprise lending, financial inclusion, and a parent group with a strong impact-banking tradition.</t>
+          <t>One of the more sustainability-forward Egyptian banks, with a dedicated sustainability function and published commitments.</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>Borrower quality, default reduction through better-prepared businesses, and group impact reporting.</t>
+          <t>Sustainability reporting content and visible youth impact.</t>
         </is>
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>Head of micro and small enterprises, with CSR as co-sponsor</t>
+          <t>Chief sustainability officer or head of sustainable development</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>Through the micro and small enterprise business line, where the commercial case is strongest.</t>
+          <t>Direct, through the sustainability function rather than marketing.</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>Calendar year, with group reporting in the first quarter.</t>
+          <t>Calendar year.</t>
         </is>
       </c>
       <c r="N16" s="11" t="inlineStr">
@@ -2355,7 +2349,7 @@
       </c>
       <c r="P16" s="10" t="inlineStr">
         <is>
-          <t>Commercial logic strong; programme not confirmed.</t>
+          <t>Sustainability positioning is established; the specific budget line is unconfirmed.</t>
         </is>
       </c>
       <c r="Q16" s="13" t="inlineStr">
@@ -2369,7 +2363,7 @@
       <c r="U16" s="14" t="n"/>
       <c r="V16" s="14" t="n"/>
     </row>
-    <row r="17" ht="61" customHeight="1">
+    <row r="17" ht="48.8" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -2377,58 +2371,58 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Banque du Caire</t>
+          <t>Bank of Alexandria (Intesa Sanpaolo)</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>Banking, state-owned</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>National, strong governorate footprint</t>
+          <t>National</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Microfinance at scale, financial inclusion, and community CSR.</t>
+          <t>Micro and small enterprise lending, financial inclusion, and a parent group with a strong impact-banking tradition.</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>Better-prepared microfinance borrowers and inclusion numbers.</t>
+          <t>Borrower quality, default reduction through better-prepared businesses, and group impact reporting.</t>
         </is>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>Head of microfinance, with CSR as secondary</t>
+          <t>Head of micro and small enterprises, with CSR as co-sponsor</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>Through the microfinance business line.</t>
+          <t>Through the micro and small enterprise business line, where the commercial case is strongest.</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>State-linked fiscal year from July.</t>
+          <t>Calendar year, with group reporting in the first quarter.</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
@@ -2443,7 +2437,7 @@
       </c>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>Microfinance scale is well established; programme fit is a proposal.</t>
+          <t>Commercial logic strong; programme not confirmed.</t>
         </is>
       </c>
       <c r="Q17" s="13" t="inlineStr">
@@ -2457,7 +2451,7 @@
       <c r="U17" s="14" t="n"/>
       <c r="V17" s="14" t="n"/>
     </row>
-    <row r="18" ht="61" customHeight="1">
+    <row r="18" ht="48.8" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -2465,53 +2459,53 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Export Development Bank of Egypt (EBank)</t>
+          <t>Banque du Caire</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>Development banking</t>
+          <t>Banking, state-owned</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>National, strong governorate footprint</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>SME and export development mandate, with sustainability and entrepreneurship support attached to it.</t>
+          <t>Microfinance at scale, financial inclusion, and community CSR.</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>SME development numbers against a public mandate.</t>
+          <t>Better-prepared microfinance borrowers and inclusion numbers.</t>
         </is>
       </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
-          <t>Head of sustainability or SME development</t>
+          <t>Head of microfinance, with CSR as secondary</t>
         </is>
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>Direct, through the SME or sustainable development function.</t>
+          <t>Through the microfinance business line.</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
@@ -2531,7 +2525,7 @@
       </c>
       <c r="P18" s="10" t="inlineStr">
         <is>
-          <t>Mandate is clear; programme fit to be confirmed.</t>
+          <t>Microfinance scale is well established; programme fit is a proposal.</t>
         </is>
       </c>
       <c r="Q18" s="13" t="inlineStr">
@@ -2545,7 +2539,7 @@
       <c r="U18" s="14" t="n"/>
       <c r="V18" s="14" t="n"/>
     </row>
-    <row r="19" ht="61" customHeight="1">
+    <row r="19" ht="48.8" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -2553,18 +2547,18 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>ExxonMobil Egypt</t>
+          <t>Credit Agricole Egypt</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Oil, gas and lubricants</t>
+          <t>Banking, international</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
@@ -2574,32 +2568,32 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>Corporate citizenship covering education, women's economic opportunity and community investment. Named in this plan's partner list for competition sponsorship.</t>
+          <t>A structured CSR programme covering education, environment and community development, reported to the French parent.</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>Women's economic empowerment numbers, and visible community investment.</t>
+          <t>Documented social impact for group reporting.</t>
         </is>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>Public and government affairs manager</t>
+          <t>CSR manager</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>Direct to public and government affairs. AmCham Egypt is the warm route, where they are an active member.</t>
+          <t>Direct. Their CSR function is comparatively accessible.</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
@@ -2619,7 +2613,7 @@
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>Corporate citizenship themes are stable globally; the Egypt budget line is unconfirmed.</t>
+          <t>CSR function established; specific fit unconfirmed.</t>
         </is>
       </c>
       <c r="Q19" s="13" t="inlineStr">
@@ -2633,7 +2627,7 @@
       <c r="U19" s="14" t="n"/>
       <c r="V19" s="14" t="n"/>
     </row>
-    <row r="20" ht="61" customHeight="1">
+    <row r="20" ht="73.19999999999999" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -2641,58 +2635,58 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>HSBC Egypt</t>
+          <t>Etisalat by e&amp; Egypt</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr"/>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Banking, international</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>Greater Cairo and Alexandria</t>
+          <t>National</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>Future Skills and education grants under a global community investment framework, run through registered NGO partners.</t>
+          <t>Digital inclusion, education and youth programmes under the group's sustainability framework.</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>Employability and future skills outcomes that roll into global community investment reporting.</t>
+          <t>A programme of its own rather than a share of someone else's, and numbers that stand up in the group sustainability report.</t>
         </is>
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>Head of corporate sustainability, Egypt</t>
+          <t>Sustainability or corporate communications manager</t>
         </is>
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>Annual grant cycle through the corporate sustainability team. An existing grantee NGO as co-applicant materially improves the odds.</t>
+          <t>Corporate sustainability contact on the e&amp; Egypt site; the UAE parent publishes the group framework the local report rolls into.</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>Grant cycles typically open once a year. Ask the timing early.</t>
+          <t>Calendar year, with group reporting pressure in the fourth quarter.</t>
         </is>
       </c>
       <c r="N20" s="11" t="inlineStr">
@@ -2707,7 +2701,7 @@
       </c>
       <c r="P20" s="10" t="inlineStr">
         <is>
-          <t>Global framework is stable; the Egypt cycle and themes need confirming each year.</t>
+          <t>Entity and CSR theme are established; no current entrepreneurship programme confirmed in this session. Treat the programme angle as a proposal, not as a response to something they run.</t>
         </is>
       </c>
       <c r="Q20" s="13" t="inlineStr">
@@ -2721,7 +2715,7 @@
       <c r="U20" s="14" t="n"/>
       <c r="V20" s="14" t="n"/>
     </row>
-    <row r="21" ht="61" customHeight="1">
+    <row r="21" ht="48.8" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -2729,18 +2723,18 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Mansour Foundation for Development</t>
+          <t>Eva Pharma</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Family foundation</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
@@ -2750,37 +2744,37 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>Family philanthropy linked to the Mansour Group, covering education, health and community development.</t>
+          <t>A notably active corporate social programme covering health access, capacity building and youth development, with an Africa dimension.</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>Family legacy, education outcomes, and national reach.</t>
+          <t>Capability built, youth developed, and an Africa and Egypt story.</t>
         </is>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>Executive director</t>
+          <t>Head of corporate social responsibility</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>Through the Egyptian Businessmen's Association or a board-level introduction. Cold approaches to family foundations rarely work.</t>
+          <t>Direct. They are approachable and comparatively fast.</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>Relationship-driven rather than cyclical.</t>
+          <t>Calendar year.</t>
         </is>
       </c>
       <c r="N21" s="11" t="inlineStr">
@@ -2788,14 +2782,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="O21" s="16" t="inlineStr">
-        <is>
-          <t>low</t>
+      <c r="O21" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>The foundation's existence and themes need verifying before approaching.</t>
+          <t>CSR activity is well established; the entrepreneurship fit is a proposal.</t>
         </is>
       </c>
       <c r="Q21" s="13" t="inlineStr">
@@ -2809,7 +2803,7 @@
       <c r="U21" s="14" t="n"/>
       <c r="V21" s="14" t="n"/>
     </row>
-    <row r="22" ht="61" customHeight="1">
+    <row r="22" ht="48.8" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -2817,18 +2811,18 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Mansour Group</t>
+          <t>Export Development Bank of Egypt (EBank)</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr"/>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Diversified: distribution, retail, automotive</t>
+          <t>Development banking</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
@@ -2838,37 +2832,37 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Large family group with retail, distribution and automotive arms, and an associated family philanthropic tradition.</t>
+          <t>SME and export development mandate, with sustainability and entrepreneurship support attached to it.</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>Micro-retailer capability, family legacy, and national reach.</t>
+          <t>SME development numbers against a public mandate.</t>
         </is>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>Group corporate affairs, with the family foundation separately</t>
+          <t>Head of sustainability or SME development</t>
         </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>Through the Egyptian Businessmen's Association or AmCham, where the group is prominent.</t>
+          <t>Direct, through the SME or sustainable development function.</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>Calendar year.</t>
+          <t>State-linked fiscal year from July.</t>
         </is>
       </c>
       <c r="N22" s="11" t="inlineStr">
@@ -2876,14 +2870,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="O22" s="16" t="inlineStr">
-        <is>
-          <t>low</t>
+      <c r="O22" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="P22" s="10" t="inlineStr">
         <is>
-          <t>The group's scale is certain; the philanthropic route and its current priorities need verifying.</t>
+          <t>Mandate is clear; programme fit to be confirmed.</t>
         </is>
       </c>
       <c r="Q22" s="13" t="inlineStr">
@@ -2897,7 +2891,7 @@
       <c r="U22" s="14" t="n"/>
       <c r="V22" s="14" t="n"/>
     </row>
-    <row r="23" ht="73.19999999999999" customHeight="1">
+    <row r="23" ht="61" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -2905,18 +2899,18 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Microsoft Egypt</t>
+          <t>ExxonMobil Egypt</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr"/>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Oil, gas and lubricants</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
@@ -2926,37 +2920,37 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>Skills initiatives, nonprofit grants and cloud credits, with employability as the stated outcome.</t>
+          <t>Corporate citizenship covering education, women's economic opportunity and community investment. Named in this plan's partner list for competition sponsorship.</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>Measurable skilling numbers, a credible local implementer, and alignment with their own skilling taxonomy.</t>
+          <t>Women's economic empowerment numbers, and visible community investment.</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>Philanthropies or corporate social responsibility lead for the Middle East and Africa, with the Egypt country team sponsoring</t>
+          <t>Public and government affairs manager</t>
         </is>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>Microsoft philanthropies works through registered nonprofits: the cleanest route is as the delivery partner of an NGO already in their grantee list.</t>
+          <t>Direct to public and government affairs. AmCham Egypt is the warm route, where they are an active member.</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>Microsoft's financial year begins in July, so the proposal window is March to May.</t>
+          <t>Calendar year.</t>
         </is>
       </c>
       <c r="N23" s="11" t="inlineStr">
@@ -2971,7 +2965,7 @@
       </c>
       <c r="P23" s="10" t="inlineStr">
         <is>
-          <t>Global programme structure is stable; the Egypt-specific budget line is not confirmed here.</t>
+          <t>Corporate citizenship themes are stable globally; the Egypt budget line is unconfirmed.</t>
         </is>
       </c>
       <c r="Q23" s="13" t="inlineStr">
@@ -2985,7 +2979,7 @@
       <c r="U23" s="14" t="n"/>
       <c r="V23" s="14" t="n"/>
     </row>
-    <row r="24" ht="61" customHeight="1">
+    <row r="24" ht="48.8" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -2993,18 +2987,18 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Orascom Construction and the Sawiris family companies</t>
+          <t>Fawry</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -3014,37 +3008,37 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>Technical training and construction skills programmes, alongside the family's separate philanthropic vehicles.</t>
+          <t>Financial inclusion, merchant enablement and SME digitisation, with a CSR narrative built around small business.</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>A skilled trade pipeline and demonstrable local employment.</t>
+          <t>Merchant acquisition that looks like social impact, and SME formalisation numbers.</t>
         </is>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>Corporate communications, with the technical training function as the operational counterpart</t>
+          <t>Marketing or sustainability director</t>
         </is>
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>Approach the technical training function first. The Sawiris Foundation is a separate organisation and a separate ask.</t>
+          <t>Direct, through corporate communications. Their SME team is the stronger internal sponsor than CSR.</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>Calendar year.</t>
+          <t>Calendar year, with budget set in the fourth quarter.</t>
         </is>
       </c>
       <c r="N24" s="11" t="inlineStr">
@@ -3059,7 +3053,7 @@
       </c>
       <c r="P24" s="10" t="inlineStr">
         <is>
-          <t>Technical training activity is established in the sector; the specific programme is unconfirmed.</t>
+          <t>Commercial logic is strong; the CSR budget line is not confirmed.</t>
         </is>
       </c>
       <c r="Q24" s="13" t="inlineStr">
@@ -3081,58 +3075,58 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>PepsiCo Egypt</t>
+          <t>HSBC Egypt</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Food and beverage</t>
+          <t>Banking, international</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>National, with Upper Egypt agricultural presence</t>
+          <t>Greater Cairo and Alexandria</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>PepsiCo Foundation and local community investment, covering agriculture, water, women's economic empowerment and youth.</t>
+          <t>Future Skills and education grants under a global community investment framework, run through registered NGO partners.</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>Supply chain community goodwill, women's economic participation, and foundation reporting.</t>
+          <t>Employability and future skills outcomes that roll into global community investment reporting.</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>Public policy and government affairs, with the PepsiCo Foundation for larger asks</t>
+          <t>Head of corporate sustainability, Egypt</t>
         </is>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>Direct to public affairs; the foundation requires a US-facing application usually sponsored by the country team.</t>
+          <t>Annual grant cycle through the corporate sustainability team. An existing grantee NGO as co-applicant materially improves the odds.</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>Calendar year.</t>
+          <t>Grant cycles typically open once a year. Ask the timing early.</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
@@ -3147,7 +3141,7 @@
       </c>
       <c r="P25" s="10" t="inlineStr">
         <is>
-          <t>Themes are established globally and the Egyptian agricultural footprint is real; the current programme list is unconfirmed.</t>
+          <t>Global framework is stable; the Egypt cycle and themes need confirming each year.</t>
         </is>
       </c>
       <c r="Q25" s="13" t="inlineStr">
@@ -3169,18 +3163,18 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>QNB Alahli</t>
+          <t>Huawei Egypt</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr"/>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
@@ -3190,37 +3184,37 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>Education, youth and community CSR, with SME banking as a strategic commercial line.</t>
+          <t>Seeds for the Future, ICT Academy and ICT Competition, run with universities and the ICT ministry.</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>SME customer acquisition that reports as social impact.</t>
+          <t>University relationships, ministry visibility, and graduates who can be named in the programme report.</t>
         </is>
       </c>
       <c r="K26" s="10" t="inlineStr">
         <is>
-          <t>Head of communications and CSR, with SME banking as internal sponsor</t>
+          <t>Public affairs or CSR director, with the ICT Academy programme manager as the operational owner</t>
         </is>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>Direct through corporate communications, or through the Federation of Egyptian Banks working groups.</t>
+          <t>The ICT Academy university network is the route: a partner university can propose the add-on upward. ITIDA also convenes them.</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>Calendar year.</t>
+          <t>Programme cycles follow the academic year, so the window is May to August for the following year.</t>
         </is>
       </c>
       <c r="N26" s="11" t="inlineStr">
@@ -3235,7 +3229,7 @@
       </c>
       <c r="P26" s="10" t="inlineStr">
         <is>
-          <t>CSR and SME lines both established; no entrepreneurship programme confirmed in this session.</t>
+          <t>Programme names are well established regionally; confirm the Egypt cycle and the current academy partners before proposing.</t>
         </is>
       </c>
       <c r="Q26" s="13" t="inlineStr">
@@ -3257,18 +3251,18 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company and Coca-Cola Egypt</t>
+          <t>Lafarge Egypt (Holcim)</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr"/>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Cement and building materials</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
@@ -3278,37 +3272,37 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Coca-Cola Foundation grants, water stewardship, and women's economic empowerment programmes with a long history in Egypt.</t>
+          <t>Sustainability programmes including construction skills, entrepreneurship among small contractors, and community development around quarries and plants.</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>Women-owned micro-business creation, and retail network goodwill.</t>
+          <t>Small contractor capability, which converts directly into demand.</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>Public affairs, communications and sustainability manager</t>
+          <t>Sustainability manager, with the retail or small contractor sales lead</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>Direct, and through the Coca-Cola Foundation grant route for larger amounts. An existing NGO partner shortens the path.</t>
+          <t>Direct, pitching to sales and sustainability jointly.</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>Calendar year, with foundation grant cycles announced annually.</t>
+          <t>Calendar year.</t>
         </is>
       </c>
       <c r="N27" s="11" t="inlineStr">
@@ -3323,7 +3317,7 @@
       </c>
       <c r="P27" s="10" t="inlineStr">
         <is>
-          <t>Women's economic empowerment work in Egypt is well established; the current partner and cycle are unconfirmed.</t>
+          <t>The programme type is well established in the sector; the Egypt instance is unconfirmed.</t>
         </is>
       </c>
       <c r="Q27" s="13" t="inlineStr">
@@ -3337,7 +3331,7 @@
       <c r="U27" s="14" t="n"/>
       <c r="V27" s="14" t="n"/>
     </row>
-    <row r="28" ht="61" customHeight="1">
+    <row r="28" ht="48.8" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -3345,18 +3339,18 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>TotalEnergies Egypt</t>
+          <t>Mansour Foundation for Development</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>Energy and fuel retail</t>
+          <t>Family foundation</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
@@ -3366,37 +3360,37 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>A corporate foundation with youth inclusion and education as stated priorities, plus road safety and energy access.</t>
+          <t>Family philanthropy linked to the Mansour Group, covering education, health and community development.</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>Youth inclusion outcomes documented to foundation standards.</t>
+          <t>Family legacy, education outcomes, and national reach.</t>
         </is>
       </c>
       <c r="K28" s="10" t="inlineStr">
         <is>
-          <t>Foundation or CSR coordinator, Egypt, reporting to the group foundation</t>
+          <t>Executive director</t>
         </is>
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
-          <t>Direct, through the Egypt corporate affairs function, which routes to the group foundation.</t>
+          <t>Through the Egyptian Businessmen's Association or a board-level introduction. Cold approaches to family foundations rarely work.</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>Group foundation cycles, typically annual with a documented call.</t>
+          <t>Relationship-driven rather than cyclical.</t>
         </is>
       </c>
       <c r="N28" s="11" t="inlineStr">
@@ -3404,14 +3398,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="O28" s="17" t="inlineStr">
-        <is>
-          <t>medium</t>
+      <c r="O28" s="16" t="inlineStr">
+        <is>
+          <t>low</t>
         </is>
       </c>
       <c r="P28" s="10" t="inlineStr">
         <is>
-          <t>Foundation themes are published at group level; the Egypt pipeline is unconfirmed.</t>
+          <t>The foundation's existence and themes need verifying before approaching.</t>
         </is>
       </c>
       <c r="Q28" s="13" t="inlineStr">
@@ -3425,7 +3419,7 @@
       <c r="U28" s="14" t="n"/>
       <c r="V28" s="14" t="n"/>
     </row>
-    <row r="29" ht="61" customHeight="1">
+    <row r="29" ht="48.8" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -3433,58 +3427,58 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>bp Egypt</t>
+          <t>Mansour Group</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr"/>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>Oil and gas</t>
+          <t>Diversified: distribution, retail, automotive</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>National, with a strong Mediterranean and Delta footprint</t>
+          <t>National</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Social investment tied to the communities around its operations, covering education, employability and enterprise.</t>
+          <t>Large family group with retail, distribution and automotive arms, and an associated family philanthropic tradition.</t>
         </is>
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>Licence to operate in host communities, local employment and enterprise creation near operations.</t>
+          <t>Micro-retailer capability, family legacy, and national reach.</t>
         </is>
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
-          <t>Social investment manager, with the local external affairs lead</t>
+          <t>Group corporate affairs, with the family foundation separately</t>
         </is>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>Direct to external affairs or social investment. Local governorate authorities can also refer.</t>
+          <t>Through the Egyptian Businessmen's Association or AmCham, where the group is prominent.</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>Calendar year, with multi-year social investment commitments.</t>
+          <t>Calendar year.</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
@@ -3492,14 +3486,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="O29" s="17" t="inlineStr">
-        <is>
-          <t>medium</t>
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>low</t>
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr">
         <is>
-          <t>Social investment practice is standard across their operations; the Egypt programme list is unconfirmed here.</t>
+          <t>The group's scale is certain; the philanthropic route and its current priorities need verifying.</t>
         </is>
       </c>
       <c r="Q29" s="13" t="inlineStr">
@@ -3513,7 +3507,7 @@
       <c r="U29" s="14" t="n"/>
       <c r="V29" s="14" t="n"/>
     </row>
-    <row r="30" ht="61" customHeight="1">
+    <row r="30" ht="73.19999999999999" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -3521,63 +3515,63 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Microsoft Egypt</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr"/>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Regional, with Egypt coverage</t>
+          <t>National</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>Small business enablement and financial literacy programmes across the Middle East and North Africa, usually delivered through partners.</t>
+          <t>Skills initiatives, nonprofit grants and cloud credits, with employability as the stated outcome.</t>
         </is>
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>Merchant digitisation, financial literacy reach, and a credible local delivery partner.</t>
+          <t>Measurable skilling numbers, a credible local implementer, and alignment with their own skilling taxonomy.</t>
         </is>
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>Social impact or government engagement lead for North Africa</t>
+          <t>Philanthropies or corporate social responsibility lead for the Middle East and Africa, with the Egypt country team sponsoring</t>
         </is>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>Through their Egyptian bank partners, who can sponsor the introduction, rather than cold to the regional office.</t>
+          <t>Microsoft philanthropies works through registered nonprofits: the cleanest route is as the delivery partner of an NGO already in their grantee list.</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
-          <t>Programme-driven.</t>
+          <t>Microsoft's financial year begins in July, so the proposal window is March to May.</t>
         </is>
       </c>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="O30" s="17" t="inlineStr">
@@ -3587,7 +3581,7 @@
       </c>
       <c r="P30" s="10" t="inlineStr">
         <is>
-          <t>Regional programmes are established; Egypt delivery partners and current cycle need checking.</t>
+          <t>Global programme structure is stable; the Egypt-specific budget line is not confirmed here.</t>
         </is>
       </c>
       <c r="Q30" s="13" t="inlineStr">
@@ -3609,53 +3603,53 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Madinet Masr</t>
+          <t>Orascom Construction and the Sawiris family companies</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr"/>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>Greater Cairo</t>
+          <t>National</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Community and youth programmes, and a named private-sector partner of the Orange Corners entrepreneurship programme in Egypt.</t>
+          <t>Technical training and construction skills programmes, alongside the family's separate philanthropic vehicles.</t>
         </is>
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>Association with a credible entrepreneurship programme and community development around their developments.</t>
+          <t>A skilled trade pipeline and demonstrable local employment.</t>
         </is>
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>Corporate communications or sustainability lead</t>
+          <t>Corporate communications, with the technical training function as the operational counterpart</t>
         </is>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>Through Orange Corners Egypt, where the relationship already exists.</t>
+          <t>Approach the technical training function first. The Sawiris Foundation is a separate organisation and a separate ask.</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr">
@@ -3665,17 +3659,17 @@
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="O31" s="12" t="inlineStr">
-        <is>
-          <t>high</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O31" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="P31" s="10" t="inlineStr">
         <is>
-          <t>Confirmed this session: named as a partner celebrating Orange Corners Egypt graduates in Delta and Upper Egypt.</t>
+          <t>Technical training activity is established in the sector; the specific programme is unconfirmed.</t>
         </is>
       </c>
       <c r="Q31" s="13" t="inlineStr">
@@ -3697,53 +3691,53 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Credit Agricole Egypt</t>
+          <t>PepsiCo Egypt</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr"/>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Banking, international</t>
+          <t>Food and beverage</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>National, with Upper Egypt agricultural presence</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>A structured CSR programme covering education, environment and community development, reported to the French parent.</t>
+          <t>PepsiCo Foundation and local community investment, covering agriculture, water, women's economic empowerment and youth.</t>
         </is>
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>Documented social impact for group reporting.</t>
+          <t>Supply chain community goodwill, women's economic participation, and foundation reporting.</t>
         </is>
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>CSR manager</t>
+          <t>Public policy and government affairs, with the PepsiCo Foundation for larger asks</t>
         </is>
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>Direct. Their CSR function is comparatively accessible.</t>
+          <t>Direct to public affairs; the foundation requires a US-facing application usually sponsored by the country team.</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr">
@@ -3763,7 +3757,7 @@
       </c>
       <c r="P32" s="10" t="inlineStr">
         <is>
-          <t>CSR function established; specific fit unconfirmed.</t>
+          <t>Themes are established globally and the Egyptian agricultural footprint is real; the current programme list is unconfirmed.</t>
         </is>
       </c>
       <c r="Q32" s="13" t="inlineStr">
@@ -3777,7 +3771,7 @@
       <c r="U32" s="14" t="n"/>
       <c r="V32" s="14" t="n"/>
     </row>
-    <row r="33" ht="73.19999999999999" customHeight="1">
+    <row r="33" ht="48.8" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -3785,18 +3779,18 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Etisalat by e&amp; Egypt</t>
+          <t>QNB Alahli</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr"/>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
@@ -3806,37 +3800,37 @@
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>Digital inclusion, education and youth programmes under the group's sustainability framework.</t>
+          <t>Education, youth and community CSR, with SME banking as a strategic commercial line.</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>A programme of its own rather than a share of someone else's, and numbers that stand up in the group sustainability report.</t>
+          <t>SME customer acquisition that reports as social impact.</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>Sustainability or corporate communications manager</t>
+          <t>Head of communications and CSR, with SME banking as internal sponsor</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>Corporate sustainability contact on the e&amp; Egypt site; the UAE parent publishes the group framework the local report rolls into.</t>
+          <t>Direct through corporate communications, or through the Federation of Egyptian Banks working groups.</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>Calendar year, with group reporting pressure in the fourth quarter.</t>
+          <t>Calendar year.</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
@@ -3851,7 +3845,7 @@
       </c>
       <c r="P33" s="10" t="inlineStr">
         <is>
-          <t>Entity and CSR theme are established; no current entrepreneurship programme confirmed in this session. Treat the programme angle as a proposal, not as a response to something they run.</t>
+          <t>CSR and SME lines both established; no entrepreneurship programme confirmed in this session.</t>
         </is>
       </c>
       <c r="Q33" s="13" t="inlineStr">
@@ -3873,18 +3867,18 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Eva Pharma</t>
+          <t>Telecom Egypt (WE)</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr"/>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
@@ -3894,37 +3888,37 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>A notably active corporate social programme covering health access, capacity building and youth development, with an Africa dimension.</t>
+          <t>State-linked operator with CSR anchored in digital literacy, connectivity for schools, and national initiative support.</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>Capability built, youth developed, and an Africa and Egypt story.</t>
+          <t>Alignment with national priorities and with Haya Karima style reach into underserved governorates.</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>Head of corporate social responsibility</t>
+          <t>CSR manager, under corporate communications</t>
         </is>
       </c>
       <c r="L34" s="10" t="inlineStr">
         <is>
-          <t>Direct. They are approachable and comparatively fast.</t>
+          <t>Approach through the national initiative rather than cold: a letter from Rowad 2030 or MSMEDA naming them as a partner carries further.</t>
         </is>
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>Calendar year.</t>
+          <t>State fiscal year begins in July, so proposals land best in the February to April window.</t>
         </is>
       </c>
       <c r="N34" s="11" t="inlineStr">
@@ -3939,7 +3933,7 @@
       </c>
       <c r="P34" s="10" t="inlineStr">
         <is>
-          <t>CSR activity is well established; the entrepreneurship fit is a proposal.</t>
+          <t>CSR orientation is well established; the specific programme fit is inferred from their public positioning.</t>
         </is>
       </c>
       <c r="Q34" s="13" t="inlineStr">
@@ -3953,7 +3947,7 @@
       <c r="U34" s="14" t="n"/>
       <c r="V34" s="14" t="n"/>
     </row>
-    <row r="35" ht="61" customHeight="1">
+    <row r="35" ht="48.8" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -3961,18 +3955,18 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Fawry</t>
+          <t>The Coca-Cola Company and Coca-Cola Egypt</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr"/>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
@@ -3982,37 +3976,37 @@
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>Financial inclusion, merchant enablement and SME digitisation, with a CSR narrative built around small business.</t>
+          <t>Coca-Cola Foundation grants, water stewardship, and women's economic empowerment programmes with a long history in Egypt.</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>Merchant acquisition that looks like social impact, and SME formalisation numbers.</t>
+          <t>Women-owned micro-business creation, and retail network goodwill.</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>Marketing or sustainability director</t>
+          <t>Public affairs, communications and sustainability manager</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>Direct, through corporate communications. Their SME team is the stronger internal sponsor than CSR.</t>
+          <t>Direct, and through the Coca-Cola Foundation grant route for larger amounts. An existing NGO partner shortens the path.</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
-          <t>Calendar year, with budget set in the fourth quarter.</t>
+          <t>Calendar year, with foundation grant cycles announced annually.</t>
         </is>
       </c>
       <c r="N35" s="11" t="inlineStr">
@@ -4027,7 +4021,7 @@
       </c>
       <c r="P35" s="10" t="inlineStr">
         <is>
-          <t>Commercial logic is strong; the CSR budget line is not confirmed.</t>
+          <t>Women's economic empowerment work in Egypt is well established; the current partner and cycle are unconfirmed.</t>
         </is>
       </c>
       <c r="Q35" s="13" t="inlineStr">
@@ -4041,7 +4035,7 @@
       <c r="U35" s="14" t="n"/>
       <c r="V35" s="14" t="n"/>
     </row>
-    <row r="36" ht="61" customHeight="1">
+    <row r="36" ht="48.8" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -4049,18 +4043,18 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Huawei Egypt</t>
+          <t>TotalEnergies Egypt</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr"/>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy and fuel retail</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
@@ -4070,37 +4064,37 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>Seeds for the Future, ICT Academy and ICT Competition, run with universities and the ICT ministry.</t>
+          <t>A corporate foundation with youth inclusion and education as stated priorities, plus road safety and energy access.</t>
         </is>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>University relationships, ministry visibility, and graduates who can be named in the programme report.</t>
+          <t>Youth inclusion outcomes documented to foundation standards.</t>
         </is>
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
-          <t>Public affairs or CSR director, with the ICT Academy programme manager as the operational owner</t>
+          <t>Foundation or CSR coordinator, Egypt, reporting to the group foundation</t>
         </is>
       </c>
       <c r="L36" s="10" t="inlineStr">
         <is>
-          <t>The ICT Academy university network is the route: a partner university can propose the add-on upward. ITIDA also convenes them.</t>
+          <t>Direct, through the Egypt corporate affairs function, which routes to the group foundation.</t>
         </is>
       </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
-          <t>Programme cycles follow the academic year, so the window is May to August for the following year.</t>
+          <t>Group foundation cycles, typically annual with a documented call.</t>
         </is>
       </c>
       <c r="N36" s="11" t="inlineStr">
@@ -4115,7 +4109,7 @@
       </c>
       <c r="P36" s="10" t="inlineStr">
         <is>
-          <t>Programme names are well established regionally; confirm the Egypt cycle and the current academy partners before proposing.</t>
+          <t>Foundation themes are published at group level; the Egypt pipeline is unconfirmed.</t>
         </is>
       </c>
       <c r="Q36" s="13" t="inlineStr">
@@ -4129,7 +4123,7 @@
       <c r="U36" s="14" t="n"/>
       <c r="V36" s="14" t="n"/>
     </row>
-    <row r="37" ht="61" customHeight="1">
+    <row r="37" ht="48.8" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -4137,58 +4131,58 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Lafarge Egypt (Holcim)</t>
+          <t>bp Egypt</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr"/>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>Cement and building materials</t>
+          <t>Oil and gas</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>National, with a strong Mediterranean and Delta footprint</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>Sustainability programmes including construction skills, entrepreneurship among small contractors, and community development around quarries and plants.</t>
+          <t>Social investment tied to the communities around its operations, covering education, employability and enterprise.</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>Small contractor capability, which converts directly into demand.</t>
+          <t>Licence to operate in host communities, local employment and enterprise creation near operations.</t>
         </is>
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>Sustainability manager, with the retail or small contractor sales lead</t>
+          <t>Social investment manager, with the local external affairs lead</t>
         </is>
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
-          <t>Direct, pitching to sales and sustainability jointly.</t>
+          <t>Direct to external affairs or social investment. Local governorate authorities can also refer.</t>
         </is>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>Calendar year.</t>
+          <t>Calendar year, with multi-year social investment commitments.</t>
         </is>
       </c>
       <c r="N37" s="11" t="inlineStr">
@@ -4203,7 +4197,7 @@
       </c>
       <c r="P37" s="10" t="inlineStr">
         <is>
-          <t>The programme type is well established in the sector; the Egypt instance is unconfirmed.</t>
+          <t>Social investment practice is standard across their operations; the Egypt programme list is unconfirmed here.</t>
         </is>
       </c>
       <c r="Q37" s="13" t="inlineStr">
@@ -4225,18 +4219,18 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Telecom Egypt (WE)</t>
+          <t>Abu Dhabi Islamic Bank Egypt</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr"/>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Islamic banking</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
@@ -4246,52 +4240,52 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>State-linked operator with CSR anchored in digital literacy, connectivity for schools, and national initiative support.</t>
+          <t>Community and youth CSR with a zakat and social finance dimension alongside conventional CSR.</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>Alignment with national priorities and with Haya Karima style reach into underserved governorates.</t>
+          <t>Social finance deployment that is both compliant and reportable.</t>
         </is>
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t>CSR manager, under corporate communications</t>
+          <t>Head of CSR, with sharia governance consulted on the funding route</t>
         </is>
       </c>
       <c r="L38" s="10" t="inlineStr">
         <is>
-          <t>Approach through the national initiative rather than cold: a letter from Rowad 2030 or MSMEDA naming them as a partner carries further.</t>
+          <t>Direct. Expect the sharia compliance question early and prepare for it.</t>
         </is>
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
-          <t>State fiscal year begins in July, so proposals land best in the February to April window.</t>
+          <t>Hijri and calendar considerations both apply. Ramadan is a strong giving window but a weak delivery one.</t>
         </is>
       </c>
       <c r="N38" s="11" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="O38" s="17" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O38" s="16" t="inlineStr">
+        <is>
+          <t>low</t>
         </is>
       </c>
       <c r="P38" s="10" t="inlineStr">
         <is>
-          <t>CSR orientation is well established; the specific programme fit is inferred from their public positioning.</t>
+          <t>Reasoned prospect. The social finance route needs verifying with them directly.</t>
         </is>
       </c>
       <c r="Q38" s="13" t="inlineStr">
@@ -4305,7 +4299,7 @@
       <c r="U38" s="14" t="n"/>
       <c r="V38" s="14" t="n"/>
     </row>
-    <row r="39" ht="61" customHeight="1">
+    <row r="39" ht="48.8" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -4313,18 +4307,18 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Abu Dhabi Islamic Bank Egypt</t>
+          <t>AstraZeneca Egypt</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr"/>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Islamic banking</t>
+          <t>Pharmaceuticals, international</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
@@ -4334,37 +4328,37 @@
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>Community and youth CSR with a zakat and social finance dimension alongside conventional CSR.</t>
+          <t>Young Health Programme and health system capacity work, delivered through NGO partners.</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>Social finance deployment that is both compliant and reportable.</t>
+          <t>Youth reach numbers and partner credibility.</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>Head of CSR, with sharia governance consulted on the funding route</t>
+          <t>Corporate affairs or sustainability manager</t>
         </is>
       </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
-          <t>Direct. Expect the sharia compliance question early and prepare for it.</t>
+          <t>Through their existing NGO implementing partner.</t>
         </is>
       </c>
       <c r="M39" s="10" t="inlineStr">
         <is>
-          <t>Hijri and calendar considerations both apply. Ramadan is a strong giving window but a weak delivery one.</t>
+          <t>Calendar year.</t>
         </is>
       </c>
       <c r="N39" s="11" t="inlineStr">
@@ -4379,7 +4373,7 @@
       </c>
       <c r="P39" s="10" t="inlineStr">
         <is>
-          <t>Reasoned prospect. The social finance route needs verifying with them directly.</t>
+          <t>Adjacent rather than central. Low priority.</t>
         </is>
       </c>
       <c r="Q39" s="13" t="inlineStr">
@@ -4393,7 +4387,7 @@
       <c r="U39" s="14" t="n"/>
       <c r="V39" s="14" t="n"/>
     </row>
-    <row r="40" ht="61" customHeight="1">
+    <row r="40" ht="48.8" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -4401,18 +4395,18 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>AstraZeneca Egypt</t>
+          <t>GB Corp (Ghabbour Auto)</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr"/>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>Pharmaceuticals, international</t>
+          <t>Automotive and financing</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
@@ -4422,32 +4416,32 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Young Health Programme and health system capacity work, delivered through NGO partners.</t>
+          <t>Community programmes, driver and technician training, and consumer financing with a microfinance arm.</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>Youth reach numbers and partner credibility.</t>
+          <t>Better borrowers and a skilled technician pipeline.</t>
         </is>
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>Corporate affairs or sustainability manager</t>
+          <t>CSR lead, with the microfinance business line</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr">
         <is>
-          <t>Through their existing NGO implementing partner.</t>
+          <t>Through the financing arm, where the commercial case lands.</t>
         </is>
       </c>
       <c r="M40" s="10" t="inlineStr">
@@ -4467,7 +4461,7 @@
       </c>
       <c r="P40" s="10" t="inlineStr">
         <is>
-          <t>Adjacent rather than central. Low priority.</t>
+          <t>Reasoned prospect.</t>
         </is>
       </c>
       <c r="Q40" s="13" t="inlineStr">
@@ -4481,7 +4475,7 @@
       <c r="U40" s="14" t="n"/>
       <c r="V40" s="14" t="n"/>
     </row>
-    <row r="41" ht="61" customHeight="1">
+    <row r="41" ht="48.8" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -4489,18 +4483,18 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>GB Corp (Ghabbour Auto)</t>
+          <t>Hassan Allam Holding</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr"/>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>Automotive and financing</t>
+          <t>Construction and infrastructure</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
@@ -4510,37 +4504,37 @@
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>Community programmes, driver and technician training, and consumer financing with a microfinance arm.</t>
+          <t>Community investment around projects, technical training, and a growing sustainability function.</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>Better borrowers and a skilled technician pipeline.</t>
+          <t>Community acceptance around projects and local employment.</t>
         </is>
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>CSR lead, with the microfinance business line</t>
+          <t>Sustainability or corporate communications lead</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr">
         <is>
-          <t>Through the financing arm, where the commercial case lands.</t>
+          <t>Direct, or through the project's community liaison.</t>
         </is>
       </c>
       <c r="M41" s="10" t="inlineStr">
         <is>
-          <t>Calendar year.</t>
+          <t>Project-driven rather than seasonal.</t>
         </is>
       </c>
       <c r="N41" s="11" t="inlineStr">
@@ -4569,7 +4563,7 @@
       <c r="U41" s="14" t="n"/>
       <c r="V41" s="14" t="n"/>
     </row>
-    <row r="42" ht="61" customHeight="1">
+    <row r="42" ht="48.8" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -4577,18 +4571,18 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Hassan Allam Holding</t>
+          <t>IBM Egypt</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr"/>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>Construction and infrastructure</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
@@ -4598,37 +4592,37 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>Community investment around projects, technical training, and a growing sustainability function.</t>
+          <t>SkillsBuild and corporate citizenship grants focused on employability and digital skills.</t>
         </is>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>Community acceptance around projects and local employment.</t>
+          <t>Learner numbers, certification completion, and university partners.</t>
         </is>
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>Sustainability or corporate communications lead</t>
+          <t>Corporate social responsibility lead, Egypt or Middle East and Africa</t>
         </is>
       </c>
       <c r="L42" s="10" t="inlineStr">
         <is>
-          <t>Direct, or through the project's community liaison.</t>
+          <t>Universities already inside SkillsBuild can propose the pathway upward, which is faster than a direct approach.</t>
         </is>
       </c>
       <c r="M42" s="10" t="inlineStr">
         <is>
-          <t>Project-driven rather than seasonal.</t>
+          <t>Academic year cycles.</t>
         </is>
       </c>
       <c r="N42" s="11" t="inlineStr">
@@ -4636,14 +4630,14 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O42" s="16" t="inlineStr">
-        <is>
-          <t>low</t>
+      <c r="O42" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="P42" s="10" t="inlineStr">
         <is>
-          <t>Reasoned prospect.</t>
+          <t>SkillsBuild is a stable global programme; the Egypt partner list needs checking.</t>
         </is>
       </c>
       <c r="Q42" s="13" t="inlineStr">
@@ -4657,7 +4651,7 @@
       <c r="U42" s="14" t="n"/>
       <c r="V42" s="14" t="n"/>
     </row>
-    <row r="43" ht="61" customHeight="1">
+    <row r="43" ht="48.8" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -4665,58 +4659,58 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>IBM Egypt</t>
+          <t>Juhayna Food Industries</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr"/>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Dairy and juice</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>National, with agricultural supply chain</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>SkillsBuild and corporate citizenship grants focused on employability and digital skills.</t>
+          <t>Agricultural development, farmer support and community programmes, with a family foundation tradition behind the company.</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>Learner numbers, certification completion, and university partners.</t>
+          <t>Supply chain resilience and rural livelihoods.</t>
         </is>
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>Corporate social responsibility lead, Egypt or Middle East and Africa</t>
+          <t>Corporate affairs, with the family foundation for larger asks</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
-          <t>Universities already inside SkillsBuild can propose the pathway upward, which is faster than a direct approach.</t>
+          <t>Direct, or through the Egyptian Junior Business Association network where the family is active.</t>
         </is>
       </c>
       <c r="M43" s="10" t="inlineStr">
         <is>
-          <t>Academic year cycles.</t>
+          <t>Calendar year.</t>
         </is>
       </c>
       <c r="N43" s="11" t="inlineStr">
@@ -4731,7 +4725,7 @@
       </c>
       <c r="P43" s="10" t="inlineStr">
         <is>
-          <t>SkillsBuild is a stable global programme; the Egypt partner list needs checking.</t>
+          <t>Agricultural community work is established; the entrepreneurship angle is a proposal.</t>
         </is>
       </c>
       <c r="Q43" s="13" t="inlineStr">
@@ -4745,7 +4739,7 @@
       <c r="U43" s="14" t="n"/>
       <c r="V43" s="14" t="n"/>
     </row>
-    <row r="44" ht="61" customHeight="1">
+    <row r="44" ht="48.8" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -4753,58 +4747,58 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Juhayna Food Industries</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr"/>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>Dairy and juice</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>National, with agricultural supply chain</t>
+          <t>Regional, with Egypt coverage</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>Agricultural development, farmer support and community programmes, with a family foundation tradition behind the company.</t>
+          <t>Boost with Meta and small business training programmes, usually delivered through local implementing partners.</t>
         </is>
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>Supply chain resilience and rural livelihoods.</t>
+          <t>Small business reach numbers and local language delivery.</t>
         </is>
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>Corporate affairs, with the family foundation for larger asks</t>
+          <t>Public policy or community partnerships manager for North Africa</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr">
         <is>
-          <t>Direct, or through the Egyptian Junior Business Association network where the family is active.</t>
+          <t>Through an existing implementing partner. Direct approaches to Meta without one rarely land.</t>
         </is>
       </c>
       <c r="M44" s="10" t="inlineStr">
         <is>
-          <t>Calendar year.</t>
+          <t>Programme-driven rather than seasonal.</t>
         </is>
       </c>
       <c r="N44" s="11" t="inlineStr">
@@ -4812,14 +4806,14 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O44" s="17" t="inlineStr">
-        <is>
-          <t>medium</t>
+      <c r="O44" s="16" t="inlineStr">
+        <is>
+          <t>low</t>
         </is>
       </c>
       <c r="P44" s="10" t="inlineStr">
         <is>
-          <t>Agricultural community work is established; the entrepreneurship angle is a proposal.</t>
+          <t>Fit is reasoned, not confirmed. Verify that the Egypt programme is still running before investing time.</t>
         </is>
       </c>
       <c r="Q44" s="13" t="inlineStr">
@@ -4833,7 +4827,7 @@
       <c r="U44" s="14" t="n"/>
       <c r="V44" s="14" t="n"/>
     </row>
-    <row r="45" ht="61" customHeight="1">
+    <row r="45" ht="48.8" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -4841,58 +4835,58 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>SODIC</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr"/>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Regional, with Egypt coverage</t>
+          <t>Greater Cairo and North Coast</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>Boost with Meta and small business training programmes, usually delivered through local implementing partners.</t>
+          <t>Education and community CSR, with a record of funding named education initiatives.</t>
         </is>
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>Small business reach numbers and local language delivery.</t>
+          <t>Brand association with quality education and community impact.</t>
         </is>
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>Public policy or community partnerships manager for North Africa</t>
+          <t>Marketing and communications director</t>
         </is>
       </c>
       <c r="L45" s="10" t="inlineStr">
         <is>
-          <t>Through an existing implementing partner. Direct approaches to Meta without one rarely land.</t>
+          <t>Direct. Developer marketing budgets move faster than CSR budgets.</t>
         </is>
       </c>
       <c r="M45" s="10" t="inlineStr">
         <is>
-          <t>Programme-driven rather than seasonal.</t>
+          <t>Calendar year.</t>
         </is>
       </c>
       <c r="N45" s="11" t="inlineStr">
@@ -4900,14 +4894,14 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O45" s="16" t="inlineStr">
-        <is>
-          <t>low</t>
+      <c r="O45" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="P45" s="10" t="inlineStr">
         <is>
-          <t>Fit is reasoned, not confirmed. Verify that the Egypt programme is still running before investing time.</t>
+          <t>Education CSR is established; fit is a proposal.</t>
         </is>
       </c>
       <c r="Q45" s="13" t="inlineStr">
@@ -4921,7 +4915,7 @@
       <c r="U45" s="14" t="n"/>
       <c r="V45" s="14" t="n"/>
     </row>
-    <row r="46" ht="61" customHeight="1">
+    <row r="46" ht="48.8" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -4929,53 +4923,53 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>SODIC</t>
+          <t>Schlumberger (SLB) Egypt</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr"/>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Oilfield services</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>Greater Cairo and North Coast</t>
+          <t>National</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>Education and community CSR, with a record of funding named education initiatives.</t>
+          <t>STEM education, technical training and community programmes near operations.</t>
         </is>
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>Brand association with quality education and community impact.</t>
+          <t>Technical talent pipeline and STEM outcomes.</t>
         </is>
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>Marketing and communications director</t>
+          <t>Community affairs or HR community programmes lead</t>
         </is>
       </c>
       <c r="L46" s="10" t="inlineStr">
         <is>
-          <t>Direct. Developer marketing budgets move faster than CSR budgets.</t>
+          <t>Through technical institutes they already support.</t>
         </is>
       </c>
       <c r="M46" s="10" t="inlineStr">
@@ -4988,14 +4982,14 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O46" s="17" t="inlineStr">
-        <is>
-          <t>medium</t>
+      <c r="O46" s="16" t="inlineStr">
+        <is>
+          <t>low</t>
         </is>
       </c>
       <c r="P46" s="10" t="inlineStr">
         <is>
-          <t>Education CSR is established; fit is a proposal.</t>
+          <t>Reasoned prospect; no Egypt programme confirmed.</t>
         </is>
       </c>
       <c r="Q46" s="13" t="inlineStr">
@@ -5009,7 +5003,7 @@
       <c r="U46" s="14" t="n"/>
       <c r="V46" s="14" t="n"/>
     </row>
-    <row r="47" ht="61" customHeight="1">
+    <row r="47" ht="48.8" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -5017,18 +5011,18 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Schlumberger (SLB) Egypt</t>
+          <t>Talaat Moustafa Group</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr"/>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>Oilfield services</t>
+          <t>Real estate</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
@@ -5038,32 +5032,32 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>STEM education, technical training and community programmes near operations.</t>
+          <t>Large-scale community development around its cities, plus education and sports facilities.</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>Technical talent pipeline and STEM outcomes.</t>
+          <t>Occupied retail units, serviced communities, and brand.</t>
         </is>
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>Community affairs or HR community programmes lead</t>
+          <t>Corporate communications and community management</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr">
         <is>
-          <t>Through technical institutes they already support.</t>
+          <t>Through community management rather than CSR.</t>
         </is>
       </c>
       <c r="M47" s="10" t="inlineStr">
@@ -5083,7 +5077,7 @@
       </c>
       <c r="P47" s="10" t="inlineStr">
         <is>
-          <t>Reasoned prospect; no Egypt programme confirmed.</t>
+          <t>Reasoned prospect.</t>
         </is>
       </c>
       <c r="Q47" s="13" t="inlineStr">
@@ -5097,7 +5091,7 @@
       <c r="U47" s="14" t="n"/>
       <c r="V47" s="14" t="n"/>
     </row>
-    <row r="48" ht="61" customHeight="1">
+    <row r="48" ht="48.8" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -5105,18 +5099,18 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Talaat Moustafa Group</t>
+          <t>Unilever Mashreq</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr"/>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>Real estate</t>
+          <t>Consumer goods</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
@@ -5126,32 +5120,32 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>Large-scale community development around its cities, plus education and sports facilities.</t>
+          <t>Sustainable living programmes, women's empowerment through distribution networks, and youth skilling.</t>
         </is>
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>Occupied retail units, serviced communities, and brand.</t>
+          <t>Distributor network growth that reads as empowerment, plus skilling numbers.</t>
         </is>
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>Corporate communications and community management</t>
+          <t>Sustainability or corporate affairs manager</t>
         </is>
       </c>
       <c r="L48" s="10" t="inlineStr">
         <is>
-          <t>Through community management rather than CSR.</t>
+          <t>Direct to corporate affairs.</t>
         </is>
       </c>
       <c r="M48" s="10" t="inlineStr">
@@ -5171,7 +5165,7 @@
       </c>
       <c r="P48" s="10" t="inlineStr">
         <is>
-          <t>Reasoned prospect.</t>
+          <t>Reasoned prospect based on their model elsewhere.</t>
         </is>
       </c>
       <c r="Q48" s="13" t="inlineStr">
@@ -5185,7 +5179,7 @@
       <c r="U48" s="14" t="n"/>
       <c r="V48" s="14" t="n"/>
     </row>
-    <row r="49" ht="61" customHeight="1">
+    <row r="49" ht="48.8" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -5193,58 +5187,58 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Unilever Mashreq</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr"/>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>Consumer goods</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Regional, with Egypt coverage</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>Sustainable living programmes, women's empowerment through distribution networks, and youth skilling.</t>
+          <t>Small business enablement and financial literacy programmes across the Middle East and North Africa, usually delivered through partners.</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>Distributor network growth that reads as empowerment, plus skilling numbers.</t>
+          <t>Merchant digitisation, financial literacy reach, and a credible local delivery partner.</t>
         </is>
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>Sustainability or corporate affairs manager</t>
+          <t>Social impact or government engagement lead for North Africa</t>
         </is>
       </c>
       <c r="L49" s="10" t="inlineStr">
         <is>
-          <t>Direct to corporate affairs.</t>
+          <t>Through their Egyptian bank partners, who can sponsor the introduction, rather than cold to the regional office.</t>
         </is>
       </c>
       <c r="M49" s="10" t="inlineStr">
         <is>
-          <t>Calendar year.</t>
+          <t>Programme-driven.</t>
         </is>
       </c>
       <c r="N49" s="11" t="inlineStr">
@@ -5252,14 +5246,14 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O49" s="16" t="inlineStr">
-        <is>
-          <t>low</t>
+      <c r="O49" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="P49" s="10" t="inlineStr">
         <is>
-          <t>Reasoned prospect based on their model elsewhere.</t>
+          <t>Regional programmes are established; Egypt delivery partners and current cycle need checking.</t>
         </is>
       </c>
       <c r="Q49" s="13" t="inlineStr">
@@ -5273,7 +5267,7 @@
       <c r="U49" s="14" t="n"/>
       <c r="V49" s="14" t="n"/>
     </row>
-    <row r="50" ht="61" customHeight="1">
+    <row r="50" ht="48.8" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -5281,7 +5275,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
@@ -5302,12 +5296,12 @@
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -5369,7 +5363,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Mission Partner or in-kind</t>
+          <t>Supporting Partner</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -5390,12 +5384,12 @@
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -5449,7 +5443,7 @@
       <c r="U51" s="14" t="n"/>
       <c r="V51" s="14" t="n"/>
     </row>
-    <row r="52" ht="61" customHeight="1">
+    <row r="52" ht="48.8" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -5457,7 +5451,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Mission Partner or in-kind</t>
+          <t>Supporting Partner</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
@@ -5478,12 +5472,12 @@
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -5537,7 +5531,7 @@
       <c r="U52" s="14" t="n"/>
       <c r="V52" s="14" t="n"/>
     </row>
-    <row r="53" ht="61" customHeight="1">
+    <row r="53" ht="48.8" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -5545,7 +5539,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Mission Partner or in-kind</t>
+          <t>Supporting Partner</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -5566,12 +5560,12 @@
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -5625,7 +5619,7 @@
       <c r="U53" s="14" t="n"/>
       <c r="V53" s="14" t="n"/>
     </row>
-    <row r="54" ht="61" customHeight="1">
+    <row r="54" ht="48.8" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -5633,7 +5627,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Mission Partner or in-kind</t>
+          <t>Supporting Partner</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
@@ -5654,12 +5648,12 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -5713,7 +5707,7 @@
       <c r="U54" s="14" t="n"/>
       <c r="V54" s="14" t="n"/>
     </row>
-    <row r="55" ht="61" customHeight="1">
+    <row r="55" ht="48.8" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -5721,7 +5715,7 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Mission Partner or in-kind</t>
+          <t>Supporting Partner</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
@@ -5742,12 +5736,12 @@
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -5809,7 +5803,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Mission Partner or in-kind</t>
+          <t>Supporting Partner</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
@@ -5830,12 +5824,12 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>Cash, in-kind, mentors</t>
+          <t>Cash or in-kind reach</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>A named tier in the coalition: a governorate, a sector or one of the fifteen missions under their name, with the direction report and the closing report.</t>
+          <t>A named tier in the coalition, webinars under their name, the direction report before it is published, and the closing report.</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -5918,12 +5912,12 @@
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
@@ -6006,12 +6000,12 @@
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -6098,12 +6092,12 @@
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -6190,12 +6184,12 @@
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -6278,12 +6272,12 @@
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -6366,12 +6360,12 @@
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -6454,12 +6448,12 @@
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -6542,12 +6536,12 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
@@ -6601,7 +6595,7 @@
       <c r="U64" s="14" t="n"/>
       <c r="V64" s="14" t="n"/>
     </row>
-    <row r="65" ht="61" customHeight="1">
+    <row r="65" ht="48.8" customHeight="1">
       <c r="A65" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -6630,12 +6624,12 @@
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
@@ -6718,12 +6712,12 @@
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -6806,12 +6800,12 @@
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
@@ -6865,7 +6859,7 @@
       <c r="U67" s="14" t="n"/>
       <c r="V67" s="14" t="n"/>
     </row>
-    <row r="68" ht="61" customHeight="1">
+    <row r="68" ht="48.8" customHeight="1">
       <c r="A68" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -6894,12 +6888,12 @@
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
@@ -6953,7 +6947,7 @@
       <c r="U68" s="14" t="n"/>
       <c r="V68" s="14" t="n"/>
     </row>
-    <row r="69" ht="61" customHeight="1">
+    <row r="69" ht="48.8" customHeight="1">
       <c r="A69" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -6982,12 +6976,12 @@
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
@@ -7041,7 +7035,7 @@
       <c r="U69" s="14" t="n"/>
       <c r="V69" s="14" t="n"/>
     </row>
-    <row r="70" ht="61" customHeight="1">
+    <row r="70" ht="48.8" customHeight="1">
       <c r="A70" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -7070,12 +7064,12 @@
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -7129,7 +7123,7 @@
       <c r="U70" s="14" t="n"/>
       <c r="V70" s="14" t="n"/>
     </row>
-    <row r="71" ht="61" customHeight="1">
+    <row r="71" ht="48.8" customHeight="1">
       <c r="A71" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -7158,12 +7152,12 @@
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -7217,7 +7211,7 @@
       <c r="U71" s="14" t="n"/>
       <c r="V71" s="14" t="n"/>
     </row>
-    <row r="72" ht="61" customHeight="1">
+    <row r="72" ht="48.8" customHeight="1">
       <c r="A72" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -7246,12 +7240,12 @@
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -7313,7 +7307,7 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
@@ -7334,12 +7328,12 @@
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
@@ -7401,7 +7395,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
@@ -7422,12 +7416,12 @@
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
@@ -7481,7 +7475,7 @@
       <c r="U74" s="14" t="n"/>
       <c r="V74" s="14" t="n"/>
     </row>
-    <row r="75" ht="61" customHeight="1">
+    <row r="75" ht="48.8" customHeight="1">
       <c r="A75" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -7489,7 +7483,7 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
@@ -7510,12 +7504,12 @@
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
@@ -7577,7 +7571,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -7598,12 +7592,12 @@
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
@@ -7665,7 +7659,7 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -7686,12 +7680,12 @@
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
@@ -7753,7 +7747,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -7774,12 +7768,12 @@
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
@@ -7841,7 +7835,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
@@ -7866,12 +7860,12 @@
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -7933,7 +7927,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
@@ -7954,12 +7948,12 @@
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
@@ -8021,7 +8015,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -8042,12 +8036,12 @@
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
@@ -8101,7 +8095,7 @@
       <c r="U81" s="14" t="n"/>
       <c r="V81" s="14" t="n"/>
     </row>
-    <row r="82" ht="61" customHeight="1">
+    <row r="82" ht="48.8" customHeight="1">
       <c r="A82" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -8109,7 +8103,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -8130,12 +8124,12 @@
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
@@ -8197,58 +8191,58 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Enabel, SIDA, Danida, Swiss SDC and the smaller bilateral agencies</t>
+          <t>Alashanek ya Balady Association for Sustainable Development (AYB-SD)</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr"/>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>Bilateral development cooperation</t>
+          <t>Youth and livelihoods NGO</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Greater Cairo and several governorates</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>Employment, skills, governance and private sector programmes, each with a modest Egypt portfolio but a lower barrier to entry than the largest donors.</t>
+          <t>Started as a student initiative and became a development NGO focused on employability, vocational training and small enterprise for low-income young people.</t>
         </is>
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>Results inside a narrow thematic mandate, and low fiduciary risk.</t>
+          <t>Job placement and income improvement for low-income youth.</t>
         </is>
       </c>
       <c r="K83" s="10" t="inlineStr">
         <is>
-          <t>Programme officer at the relevant embassy or agency office</t>
+          <t>Programme director</t>
         </is>
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>Through the embassies' development sections. Several publish calls.</t>
+          <t>Direct.</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr">
         <is>
-          <t>Varies by agency; most plan annually.</t>
+          <t>Project-driven.</t>
         </is>
       </c>
       <c r="N83" s="11" t="inlineStr">
@@ -8256,14 +8250,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="O83" s="16" t="inlineStr">
-        <is>
-          <t>low</t>
+      <c r="O83" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="P83" s="10" t="inlineStr">
         <is>
-          <t>Grouped deliberately. Verify which of these currently fund employment work in Egypt before allocating time.</t>
+          <t>Organisation and focus are well established; this session's search returned nothing current, so verify before approaching.</t>
         </is>
       </c>
       <c r="Q83" s="13" t="inlineStr">
@@ -8277,7 +8271,7 @@
       <c r="U83" s="14" t="n"/>
       <c r="V83" s="14" t="n"/>
     </row>
-    <row r="84" ht="61" customHeight="1">
+    <row r="84" ht="48.8" customHeight="1">
       <c r="A84" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -8285,53 +8279,53 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Mercy Corps, DRC, Terre des Hommes and the European implementers</t>
+          <t>Catholic Relief Services, Caritas Egypt and the faith-based implementers</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr"/>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>International NGO</t>
+          <t>Faith-based international NGO</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>National, strong in Upper Egypt</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>Livelihoods and economic inclusion projects funded by European donors, often covering refugees and host communities.</t>
+          <t>Livelihoods, vocational training and migrant support, with deep community networks in Upper Egypt.</t>
         </is>
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>Inclusion of refugees and host communities, and donor compliance.</t>
+          <t>Livelihoods created in the communities they serve.</t>
         </is>
       </c>
       <c r="K84" s="10" t="inlineStr">
         <is>
-          <t>Programme manager for economic recovery or livelihoods</t>
+          <t>Livelihoods programme manager</t>
         </is>
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>Direct, and through the refugee response coordination groups.</t>
+          <t>Direct. These organisations are approachable.</t>
         </is>
       </c>
       <c r="M84" s="10" t="inlineStr">
@@ -8344,14 +8338,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="O84" s="16" t="inlineStr">
-        <is>
-          <t>low</t>
+      <c r="O84" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="P84" s="10" t="inlineStr">
         <is>
-          <t>Grouped deliberately. Verify which currently operate in Egypt before allocating time.</t>
+          <t>Presence in Upper Egypt is well established; specific programmes unconfirmed.</t>
         </is>
       </c>
       <c r="Q84" s="13" t="inlineStr">
@@ -8373,73 +8367,73 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Food and Agriculture Organization (FAO) Egypt</t>
+          <t>Enabel, SIDA, Danida, Swiss SDC and the smaller bilateral agencies</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr"/>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>UN agency</t>
+          <t>Bilateral development cooperation</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>Rural Egypt, Upper Egypt and the Delta</t>
+          <t>National</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>Rural livelihoods, agribusiness development and farmer field schools.</t>
+          <t>Employment, skills, governance and private sector programmes, each with a modest Egypt portfolio but a lower barrier to entry than the largest donors.</t>
         </is>
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>Rural livelihoods and food system outcomes.</t>
+          <t>Results inside a narrow thematic mandate, and low fiduciary risk.</t>
         </is>
       </c>
       <c r="K85" s="10" t="inlineStr">
         <is>
-          <t>Programme officer for rural development</t>
+          <t>Programme officer at the relevant embassy or agency office</t>
         </is>
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>Through UNGM and the Cairo office.</t>
+          <t>Through the embassies' development sections. Several publish calls.</t>
         </is>
       </c>
       <c r="M85" s="10" t="inlineStr">
         <is>
-          <t>Project cycles.</t>
+          <t>Varies by agency; most plan annually.</t>
         </is>
       </c>
       <c r="N85" s="11" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O85" s="17" t="inlineStr">
-        <is>
-          <t>medium</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O85" s="16" t="inlineStr">
+        <is>
+          <t>low</t>
         </is>
       </c>
       <c r="P85" s="10" t="inlineStr">
         <is>
-          <t>Thematic fit is good; Egypt pipeline unconfirmed.</t>
+          <t>Grouped deliberately. Verify which of these currently fund employment work in Egypt before allocating time.</t>
         </is>
       </c>
       <c r="Q85" s="13" t="inlineStr">
@@ -8453,7 +8447,7 @@
       <c r="U85" s="14" t="n"/>
       <c r="V85" s="14" t="n"/>
     </row>
-    <row r="86" ht="61" customHeight="1">
+    <row r="86" ht="48.8" customHeight="1">
       <c r="A86" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -8461,48 +8455,48 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Alashanek ya Balady Association for Sustainable Development (AYB-SD)</t>
+          <t>Etijah, Youth and Development Consultancy Institute</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr"/>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>Youth and livelihoods NGO</t>
+          <t>Youth development NGO and consultancy</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>Greater Cairo and several governorates</t>
+          <t>National</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>Started as a student initiative and became a development NGO focused on employability, vocational training and small enterprise for low-income young people.</t>
+          <t>Youth participation, capacity building for youth organisations, and donor-funded youth programming.</t>
         </is>
       </c>
       <c r="J86" s="10" t="inlineStr">
         <is>
-          <t>Job placement and income improvement for low-income youth.</t>
+          <t>Capacity built across the youth sector, and donor results.</t>
         </is>
       </c>
       <c r="K86" s="10" t="inlineStr">
         <is>
-          <t>Programme director</t>
+          <t>Executive director</t>
         </is>
       </c>
       <c r="L86" s="10" t="inlineStr">
@@ -8520,14 +8514,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="O86" s="17" t="inlineStr">
-        <is>
-          <t>medium</t>
+      <c r="O86" s="16" t="inlineStr">
+        <is>
+          <t>low</t>
         </is>
       </c>
       <c r="P86" s="10" t="inlineStr">
         <is>
-          <t>Organisation and focus are well established; this session's search returned nothing current, so verify before approaching.</t>
+          <t>Verify current activity before approaching.</t>
         </is>
       </c>
       <c r="Q86" s="13" t="inlineStr">
@@ -8541,7 +8535,7 @@
       <c r="U86" s="14" t="n"/>
       <c r="V86" s="14" t="n"/>
     </row>
-    <row r="87" ht="61" customHeight="1">
+    <row r="87" ht="48.8" customHeight="1">
       <c r="A87" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -8549,53 +8543,53 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Catholic Relief Services, Caritas Egypt and the faith-based implementers</t>
+          <t>Mercy Corps, DRC, Terre des Hommes and the European implementers</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr"/>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>Faith-based international NGO</t>
+          <t>International NGO</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>National, strong in Upper Egypt</t>
+          <t>National</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>Livelihoods, vocational training and migrant support, with deep community networks in Upper Egypt.</t>
+          <t>Livelihoods and economic inclusion projects funded by European donors, often covering refugees and host communities.</t>
         </is>
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>Livelihoods created in the communities they serve.</t>
+          <t>Inclusion of refugees and host communities, and donor compliance.</t>
         </is>
       </c>
       <c r="K87" s="10" t="inlineStr">
         <is>
-          <t>Livelihoods programme manager</t>
+          <t>Programme manager for economic recovery or livelihoods</t>
         </is>
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>Direct. These organisations are approachable.</t>
+          <t>Direct, and through the refugee response coordination groups.</t>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr">
@@ -8608,14 +8602,14 @@
           <t>B</t>
         </is>
       </c>
-      <c r="O87" s="17" t="inlineStr">
-        <is>
-          <t>medium</t>
+      <c r="O87" s="16" t="inlineStr">
+        <is>
+          <t>low</t>
         </is>
       </c>
       <c r="P87" s="10" t="inlineStr">
         <is>
-          <t>Presence in Upper Egypt is well established; specific programmes unconfirmed.</t>
+          <t>Grouped deliberately. Verify which currently operate in Egypt before allocating time.</t>
         </is>
       </c>
       <c r="Q87" s="13" t="inlineStr">
@@ -8629,7 +8623,7 @@
       <c r="U87" s="14" t="n"/>
       <c r="V87" s="14" t="n"/>
     </row>
-    <row r="88" ht="61" customHeight="1">
+    <row r="88" ht="48.8" customHeight="1">
       <c r="A88" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -8637,18 +8631,18 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Etijah, Youth and Development Consultancy Institute</t>
+          <t>Save the Children Egypt</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr"/>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>Youth development NGO and consultancy</t>
+          <t>International NGO</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
@@ -8658,32 +8652,32 @@
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
         <is>
-          <t>Youth participation, capacity building for youth organisations, and donor-funded youth programming.</t>
+          <t>Adolescent skills, child protection and youth employability.</t>
         </is>
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>Capacity built across the youth sector, and donor results.</t>
+          <t>Adolescent outcomes with child-safe delivery.</t>
         </is>
       </c>
       <c r="K88" s="10" t="inlineStr">
         <is>
-          <t>Executive director</t>
+          <t>Programme manager for education or youth</t>
         </is>
       </c>
       <c r="L88" s="10" t="inlineStr">
         <is>
-          <t>Direct.</t>
+          <t>Direct, with safeguarding documentation ready.</t>
         </is>
       </c>
       <c r="M88" s="10" t="inlineStr">
@@ -8703,7 +8697,7 @@
       </c>
       <c r="P88" s="10" t="inlineStr">
         <is>
-          <t>Verify current activity before approaching.</t>
+          <t>Reasoned prospect; Egypt portfolio unconfirmed.</t>
         </is>
       </c>
       <c r="Q88" s="13" t="inlineStr">
@@ -8717,7 +8711,7 @@
       <c r="U88" s="14" t="n"/>
       <c r="V88" s="14" t="n"/>
     </row>
-    <row r="89" ht="61" customHeight="1">
+    <row r="89" ht="48.8" customHeight="1">
       <c r="A89" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -8725,73 +8719,73 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Save the Children Egypt</t>
+          <t>Food and Agriculture Organization (FAO) Egypt</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr"/>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>International NGO</t>
+          <t>UN agency</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Rural Egypt, Upper Egypt and the Delta</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>Adolescent skills, child protection and youth employability.</t>
+          <t>Rural livelihoods, agribusiness development and farmer field schools.</t>
         </is>
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>Adolescent outcomes with child-safe delivery.</t>
+          <t>Rural livelihoods and food system outcomes.</t>
         </is>
       </c>
       <c r="K89" s="10" t="inlineStr">
         <is>
-          <t>Programme manager for education or youth</t>
+          <t>Programme officer for rural development</t>
         </is>
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
-          <t>Direct, with safeguarding documentation ready.</t>
+          <t>Through UNGM and the Cairo office.</t>
         </is>
       </c>
       <c r="M89" s="10" t="inlineStr">
         <is>
-          <t>Project-driven.</t>
+          <t>Project cycles.</t>
         </is>
       </c>
       <c r="N89" s="11" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="O89" s="16" t="inlineStr">
-        <is>
-          <t>low</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O89" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="P89" s="10" t="inlineStr">
         <is>
-          <t>Reasoned prospect; Egypt portfolio unconfirmed.</t>
+          <t>Thematic fit is good; Egypt pipeline unconfirmed.</t>
         </is>
       </c>
       <c r="Q89" s="13" t="inlineStr">
@@ -8805,7 +8799,7 @@
       <c r="U89" s="14" t="n"/>
       <c r="V89" s="14" t="n"/>
     </row>
-    <row r="90" ht="61" customHeight="1">
+    <row r="90" ht="48.8" customHeight="1">
       <c r="A90" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -8813,7 +8807,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Mission Partner or in-kind</t>
+          <t>Supporting Partner</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
@@ -8834,12 +8828,12 @@
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
@@ -8893,7 +8887,7 @@
       <c r="U90" s="14" t="n"/>
       <c r="V90" s="14" t="n"/>
     </row>
-    <row r="91" ht="61" customHeight="1">
+    <row r="91" ht="48.8" customHeight="1">
       <c r="A91" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -8901,7 +8895,7 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>Mission Partner or in-kind</t>
+          <t>Supporting Partner</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
@@ -8922,12 +8916,12 @@
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
@@ -8981,7 +8975,7 @@
       <c r="U91" s="14" t="n"/>
       <c r="V91" s="14" t="n"/>
     </row>
-    <row r="92" ht="61" customHeight="1">
+    <row r="92" ht="48.8" customHeight="1">
       <c r="A92" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -8989,7 +8983,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Mission Partner or in-kind</t>
+          <t>Supporting Partner</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
@@ -9010,12 +9004,12 @@
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
@@ -9069,7 +9063,7 @@
       <c r="U92" s="14" t="n"/>
       <c r="V92" s="14" t="n"/>
     </row>
-    <row r="93" ht="61" customHeight="1">
+    <row r="93" ht="48.8" customHeight="1">
       <c r="A93" s="19" t="inlineStr">
         <is>
           <t>NGO and development partner</t>
@@ -9077,7 +9071,7 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>Mission Partner or in-kind</t>
+          <t>Supporting Partner</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
@@ -9098,12 +9092,12 @@
       </c>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>Reach, staff time, venues, co-funding</t>
+          <t>Reach, networks, session hosting</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>Facilitator certification for their own staff, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
+          <t>Their staff trained to host sessions, the method for their own beneficiaries, a shared evidence base, and a seat in the coalition.</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
@@ -9186,12 +9180,12 @@
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>Members, chapters, leadership. No cash</t>
+          <t>Members, chapters, ambassadors. No cash</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>The full programme free for every member, certification for ten of their leadership, their chapter on the national map, and their own chapter's data.</t>
+          <t>The full programme free for every member, ten of their leadership trained as hosts, their chapter on the national leaderboard, and their own chapter's data.</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
@@ -9274,12 +9268,12 @@
       </c>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>Members, chapters, leadership. No cash</t>
+          <t>Members, chapters, ambassadors. No cash</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>The full programme free for every member, certification for ten of their leadership, their chapter on the national map, and their own chapter's data.</t>
+          <t>The full programme free for every member, ten of their leadership trained as hosts, their chapter on the national leaderboard, and their own chapter's data.</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
@@ -9366,12 +9360,12 @@
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>Members, chapters, leadership. No cash</t>
+          <t>Members, chapters, ambassadors. No cash</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>The full programme free for every member, certification for ten of their leadership, their chapter on the national map, and their own chapter's data.</t>
+          <t>The full programme free for every member, ten of their leadership trained as hosts, their chapter on the national leaderboard, and their own chapter's data.</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
@@ -9458,12 +9452,12 @@
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>Members, chapters, leadership. No cash</t>
+          <t>Members, chapters, ambassadors. No cash</t>
         </is>
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>The full programme free for every member, certification for ten of their leadership, their chapter on the national map, and their own chapter's data.</t>
+          <t>The full programme free for every member, ten of their leadership trained as hosts, their chapter on the national leaderboard, and their own chapter's data.</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr">
@@ -9550,12 +9544,12 @@
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>Members, chapters, leadership. No cash</t>
+          <t>Members, chapters, ambassadors. No cash</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>The full programme free for every member, certification for ten of their leadership, their chapter on the national map, and their own chapter's data.</t>
+          <t>The full programme free for every member, ten of their leadership trained as hosts, their chapter on the national leaderboard, and their own chapter's data.</t>
         </is>
       </c>
       <c r="I98" s="10" t="inlineStr">
@@ -9638,12 +9632,12 @@
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>Members, chapters, leadership. No cash</t>
+          <t>Members, chapters, ambassadors. No cash</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>The full programme free for every member, certification for ten of their leadership, their chapter on the national map, and their own chapter's data.</t>
+          <t>The full programme free for every member, ten of their leadership trained as hosts, their chapter on the national leaderboard, and their own chapter's data.</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr">
@@ -9726,12 +9720,12 @@
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>Members, chapters, leadership. No cash</t>
+          <t>Members, chapters, ambassadors. No cash</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>The full programme free for every member, certification for ten of their leadership, their chapter on the national map, and their own chapter's data.</t>
+          <t>The full programme free for every member, ten of their leadership trained as hosts, their chapter on the national leaderboard, and their own chapter's data.</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr">
@@ -9814,12 +9808,12 @@
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>Members, chapters, leadership. No cash</t>
+          <t>Members, chapters, ambassadors. No cash</t>
         </is>
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>The full programme free for every member, certification for ten of their leadership, their chapter on the national map, and their own chapter's data.</t>
+          <t>The full programme free for every member, ten of their leadership trained as hosts, their chapter on the national leaderboard, and their own chapter's data.</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr">
@@ -9902,12 +9896,12 @@
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>Members, chapters, leadership. No cash</t>
+          <t>Members, chapters, ambassadors. No cash</t>
         </is>
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>The full programme free for every member, certification for ten of their leadership, their chapter on the national map, and their own chapter's data.</t>
+          <t>The full programme free for every member, ten of their leadership trained as hosts, their chapter on the national leaderboard, and their own chapter's data.</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr">
@@ -9990,12 +9984,12 @@
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>Members, chapters, leadership. No cash</t>
+          <t>Members, chapters, ambassadors. No cash</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>The full programme free for every member, certification for ten of their leadership, their chapter on the national map, and their own chapter's data.</t>
+          <t>The full programme free for every member, ten of their leadership trained as hosts, their chapter on the national leaderboard, and their own chapter's data.</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr">
@@ -10078,12 +10072,12 @@
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>Members, chapters, leadership. No cash</t>
+          <t>Members, chapters, ambassadors. No cash</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>The full programme free for every member, certification for ten of their leadership, their chapter on the national map, and their own chapter's data.</t>
+          <t>The full programme free for every member, ten of their leadership trained as hosts, their chapter on the national leaderboard, and their own chapter's data.</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
@@ -10154,7 +10148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -10186,12 +10180,12 @@
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>$40,000</t>
+          <t>$50,000</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
         <is>
-          <t>3 slots</t>
+          <t>2 slots</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
@@ -10208,11 +10202,11 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>Named as a Founding Partner of the initiative, in Arabic and English, on every surface it has: the platform, the launch, the showcase, the national report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24.8" customHeight="1">
+          <t>Named as a Founding Partner of a national initiative, in Arabic and English, in front of a million young Egyptians.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
       <c r="B6" s="25" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -10220,7 +10214,7 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>A seat on the steering committee, which sets the governorate plan and signs off the national report.</t>
+          <t>A seat on the steering committee, which sets the plan and signs off the national report.</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10226,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>A governorate or a sector of their choosing carried under their name for the whole wave.</t>
+          <t>A sector or a governorate group carried under their name for the whole wave.</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10254,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="24.8" customHeight="1">
+    <row r="10" ht="16" customHeight="1">
       <c r="B10" s="25" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -10268,11 +10262,11 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>First look at the ventures from the showcase, for their own accelerator, prize, procurement or hiring.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24.8" customHeight="1">
+          <t>Four live webinars under their name, to an audience in the tens of thousands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
       <c r="B11" s="25" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -10280,7 +10274,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Up to 40 of their staff certified as mentors and judges, with hours logged and reported back for their own employee engagement numbers.</t>
+          <t>First look at the ventures from the national showcase.</t>
         </is>
       </c>
     </row>
@@ -10292,14 +10286,14 @@
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>A closing report with named participants, completion rates, governorate and gender disaggregation, and SDG mapping, written to go straight into their own annual report.</t>
+          <t>A closing report with completion rates, governorate and gender disaggregation and SDG mapping, written to go straight into their own annual report.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -10309,7 +10303,7 @@
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>6 slots</t>
+          <t>5 slots</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -10326,7 +10320,7 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>Named as a Lead Partner across the initiative's surfaces.</t>
+          <t>Named as a Partner across the initiative's surfaces.</t>
         </is>
       </c>
     </row>
@@ -10350,7 +10344,7 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>One governorate wave or one competition season under their name.</t>
+          <t>Two live webinars under their name.</t>
         </is>
       </c>
     </row>
@@ -10374,45 +10368,45 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Up to 20 staff certified as mentors and judges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="B20" s="25" t="inlineStr">
+          <t>The closing report, disaggregated and SDG mapped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24.8" customHeight="1">
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>Supporting Partner</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>$5,000</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>10 slots</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>Cash. The entry tier, and the one a mid-sized Egyptian company or a second-tier foundation can sign inside a month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24.8" customHeight="1">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>The closing report, disaggregated and SDG mapped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>Governorate Partner</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>$8,000</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
-        <is>
-          <t>12 slots</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
-        <is>
-          <t>Cash, usually from a community investment budget tied to where they operate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24.8" customHeight="1">
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>One of the fifteen missions carried under their name, which every participant in the country passes through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
       <c r="B23" s="25" t="inlineStr">
         <is>
           <t>CSR sponsor</t>
@@ -10420,7 +10414,7 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>One named governorate for the wave, which is the version of this that an oil, cement or industrial sponsor can fund out of an existing licence-to-operate budget.</t>
+          <t>One live webinar under their name.</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10426,7 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>Two cohorts, a local showcase and a governorate report with named participants.</t>
+          <t>Their sector's slice of the direction report.</t>
         </is>
       </c>
     </row>
@@ -10444,215 +10438,133 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>The direction report for their governorate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>CSR sponsor</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>Up to 10 staff as mentors and judges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24.8" customHeight="1">
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>Mission Partner</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>$3,000</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
-        <is>
-          <t>15 slots</t>
-        </is>
-      </c>
-      <c r="E28" s="24" t="inlineStr">
-        <is>
-          <t>Cash. The entry tier, and the one a mid-sized Egyptian company or a second-tier foundation can sign inside a quarter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24.8" customHeight="1">
+          <t>Named on the platform and in the closing report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24.8" customHeight="1">
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>In-kind Partner</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>No cash</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>Uncapped</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>Reach, airtime, venues or services, valued at market rate and credited at the cash tier it matches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>CSR sponsor or NGO and development partner</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Credited at the tier their contribution values at, with the same benefits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="37.2" customHeight="1">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>CSR sponsor</t>
+          <t>CSR sponsor or NGO and development partner</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>One of the fifteen missions carried under their name, which every participant in the country passes through.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="B30" s="25" t="inlineStr">
-        <is>
-          <t>CSR sponsor</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>Their sector's slice of the direction report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>CSR sponsor</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>Named on the platform and in the closing report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
+          <t>For a telecom or a broadcaster this is the most valuable thing anyone can give this initiative, because reach is what the whole model runs on, and it is usually faster to approve than cash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>Community Supporter</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>No cash</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>Uncapped</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>Members, chapters and leadership time. No cash is asked for, ever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24.8" customHeight="1">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>CSR sponsor</t>
+          <t>Community supporter</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Staff as mentors on their own mission.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="24.8" customHeight="1">
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>In-kind Partner</t>
-        </is>
-      </c>
-      <c r="C34" s="22" t="inlineStr">
-        <is>
-          <t>No cash</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="inlineStr">
-        <is>
-          <t>Uncapped</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
-        <is>
-          <t>Anything on the in-kind menu, valued at its market rate and credited at the cash tier it matches.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24.8" customHeight="1">
+          <t>Every member gets the full fifteen-mission programme free, which everybody gets, because the whole thing is free.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24.8" customHeight="1">
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>Community supporter</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Up to 10 of their leadership trained to host info sessions and webinars, a credential they keep after their term ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>Community supporter</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Their chapter on the national leaderboard, by registrations and by completions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>CSR sponsor or NGO and development partner</t>
+          <t>Community supporter</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>Credited at the tier their contribution values at, with the same benefits. Media airtime at a rate card value of EGP 1.1 million is a Lead Partner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24.8" customHeight="1">
+          <t>Their own chapter's data: what their members are building.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>CSR sponsor or NGO and development partner</t>
+          <t>Community supporter</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>This is how a telco, a broadcaster or a venue owner joins without a cash approval, and it is usually faster.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="B38" s="21" t="inlineStr">
-        <is>
-          <t>Community Supporter</t>
-        </is>
-      </c>
-      <c r="C38" s="22" t="inlineStr">
-        <is>
-          <t>No cash</t>
-        </is>
-      </c>
-      <c r="D38" s="23" t="inlineStr">
-        <is>
-          <t>Uncapped</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
-        <is>
-          <t>Members, chapters and leadership time. No cash is asked for, ever.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="25" t="inlineStr">
-        <is>
-          <t>Community supporter</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>Every member gets the full fifteen-mission programme free for the wave.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="24.8" customHeight="1">
-      <c r="B40" s="25" t="inlineStr">
-        <is>
-          <t>Community supporter</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>Up to 10 of their leadership certified as facilitators, a credential they keep after their term ends.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="25" t="inlineStr">
-        <is>
-          <t>Community supporter</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="inlineStr">
-        <is>
-          <t>Their chapter named as a host, and their university on the national map.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="24.8" customHeight="1">
-      <c r="B42" s="25" t="inlineStr">
-        <is>
-          <t>Community supporter</t>
-        </is>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>Their own chapter's data: what their members are building, which they can show their faculty and their own sponsors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="B43" s="25" t="inlineStr">
-        <is>
-          <t>Community supporter</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>Teams going into their own competition season already through fifteen missions.</t>
         </is>
@@ -10733,7 +10645,7 @@
       </c>
       <c r="E2" s="26" t="n"/>
     </row>
-    <row r="3" ht="28" customHeight="1">
+    <row r="3" ht="37.2" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Venues and halls</t>
@@ -10746,7 +10658,7 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Every cohort needs a room for six days. A sponsor with branches in nine governorates solves delivery in nine governorates.</t>
+          <t>An info session needs a room for an evening. A sponsor with branches in nine governorates can host sessions in nine governorates, and that is the whole offline footprint of this wave.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -10930,7 +10842,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Moves facilitators and participants between governorates, which is a real line in the budget.</t>
+          <t>Gets the team to the regional showcases and the winners to the demo day.</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
@@ -10976,7 +10888,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Six-day cohorts feed people. Easy for a food company to approve.</t>
+          <t>Info sessions and showcases feed people. Easy for a food company to approve.</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
@@ -11079,7 +10991,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>The ventures that reach the showcase have been through fifteen missions, a facilitator and an AI review. A sponsor's accelerator, prize or procurement team gets a shortlist that has already been filtered by work rather than by a form.</t>
+          <t>The ventures that reach the showcase have been through fifteen missions and an AI review on every one of them. A sponsor's accelerator, prize or procurement team gets a shortlist that has already been filtered by work rather than by a form.</t>
         </is>
       </c>
     </row>
@@ -11115,7 +11027,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>A corporate that builds this alone pays for curriculum, platform, facilitator recruitment and measurement before it reaches its first participant. Joining a coalition that already has all four means the whole contribution goes to delivery.</t>
+          <t>A corporate that builds this alone pays for curriculum, platform, content and measurement before it reaches its first participant, and then reaches a few thousand people. Twenty cents a head is not a number a corporate programme can reach on its own.</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11070,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Partner staff are certified as facilitators on the same standard as everyone else. When the wave closes, the organisation still has the capability, the curriculum access and the certification, which is the opposite of how most funded projects leave their implementers.</t>
+          <t>Partner staff are trained to run info sessions and to use the curriculum with their own beneficiaries. When the wave closes the organisation still has the capability and the access, which is the opposite of how most funded projects leave their implementers.</t>
         </is>
       </c>
     </row>
@@ -11261,7 +11173,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Up to ten of a chapter's leadership are certified as facilitators on the national standard. They keep it after their term ends, and it is the first line on a CV that is otherwise all committee titles.</t>
+          <t>Up to ten of a chapter's leadership are trained to host info sessions and webinars on the national standard. They keep it after their term ends, and it is the first line on a CV that is otherwise all committee titles.</t>
         </is>
       </c>
     </row>
@@ -11498,7 +11410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -11563,7 +11475,7 @@
         </is>
       </c>
       <c r="C5" s="29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="29" t="n">
         <v>22</v>
@@ -11573,23 +11485,23 @@
         <v/>
       </c>
       <c r="F5" s="31" t="n">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="G5" s="31" t="n">
-        <v>120000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="28" t="inlineStr">
         <is>
-          <t>Lead Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C6" s="29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E6" s="30">
         <f>D6/C6</f>
@@ -11599,148 +11511,125 @@
         <v>20000</v>
       </c>
       <c r="G6" s="31" t="n">
-        <v>120000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="28" t="inlineStr">
         <is>
-          <t>Governorate Partner</t>
+          <t>Supporting Partner</t>
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E7" s="30">
         <f>D7/C7</f>
         <v/>
       </c>
       <c r="F7" s="31" t="n">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="G7" s="31" t="n">
-        <v>96000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="28" t="inlineStr">
-        <is>
-          <t>Mission Partner</t>
-        </is>
-      </c>
-      <c r="C8" s="29" t="n">
-        <v>15</v>
-      </c>
-      <c r="D8" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="33">
-        <f>D8/C8</f>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C8" s="33">
+        <f>SUM(C5:C7)</f>
         <v/>
       </c>
-      <c r="F8" s="31" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G8" s="31" t="n">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C9" s="35">
-        <f>SUM(C5:C8)</f>
+      <c r="D8" s="33">
+        <f>SUM(D5:D7)</f>
         <v/>
       </c>
-      <c r="D9" s="35">
-        <f>SUM(D5:D8)</f>
+      <c r="G8" s="33">
+        <f>SUM(G5:G7)</f>
         <v/>
       </c>
-      <c r="G9" s="35">
-        <f>SUM(G5:G8)</f>
-        <v/>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>WHERE THE RAISE STANDS</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>WHERE THE RAISE STANDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Organisations invited</t>
         </is>
       </c>
-      <c r="C12" s="37">
+      <c r="C11" s="35">
         <f>COUNTIF('INVITATION LIST'!Q2:Q104,"&lt;&gt;Not invited")</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="36" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="C13" s="37">
+      <c r="C12" s="35">
         <f>COUNTIF('INVITATION LIST'!Q2:Q104,"Signed")</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="36" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>Pledged, USD</t>
         </is>
       </c>
-      <c r="C14" s="37">
+      <c r="C13" s="35">
         <f>SUM('INVITATION LIST'!S2:S104)</f>
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>Wave 1 budget needed</t>
+        </is>
+      </c>
+      <c r="C14" s="35">
+        <f>200000.0</f>
+        <v/>
+      </c>
+    </row>
     <row r="15">
-      <c r="B15" s="36" t="inlineStr">
-        <is>
-          <t>Wave 1 budget needed</t>
-        </is>
-      </c>
-      <c r="C15" s="37">
-        <f>190500.0</f>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="C15" s="35">
+        <f>200000.0-SUM('INVITATION LIST'!S2:S104)</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="36" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="C16" s="37">
-        <f>190500.0-SUM('INVITATION LIST'!S2:S104)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>Under-covered tiers: Mission Partner. There are fewer candidates sized for these than there are slots, so either the slot count comes down or mid-sized Egyptian companies have to be added to the registry. The Mission Partner tier at $12,000 is the one a mid-cap can sign inside a quarter, and the registry is thin on mid-caps because it was built from the organisations that publish their CSR.</t>
+    <row r="17" ht="60" customHeight="1">
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>Every tier has more candidates than slots. Work the list in priority order and stop when a tier fills.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B17:G17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
